--- a/Procuring_Entities.xlsx
+++ b/Procuring_Entities.xlsx
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>COUNCIL FOR LEGAL EDUCATION</t>
+          <t>NATIONAL DROUGHT MANAGEMENT AUTHORITY</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Karen Office Park, Karen</t>
+          <t>8th Floor, Lonrho House, Standard Street</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>'254 20 266 5440</t>
+          <t>'254 20 222 7982</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>info@cle.or.ke</t>
+          <t>info@ndma.go.ke</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>NATIONAL DROUGHT MANAGEMENT AUTHORITY</t>
+          <t>PARLIAMENTARY SERVICE COMMISSION</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>8th Floor, Lonrho House, Standard Street</t>
+          <t>Parliament Buildings, Parliament Road / Junction of Parliament Rd &amp; Haile Selassie Ave</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>'254 20 222 7982</t>
+          <t>'254 20 284 8000</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>info@ndma.go.ke</t>
+          <t>clerk@parliament.go.ke</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>PARLIAMENTARY SERVICE COMMISSION</t>
+          <t>KENYA WATER INSTITUTE</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Parliament Buildings, Parliament Road / Junction of Parliament Rd &amp; Haile Selassie Ave</t>
+          <t>Ole Shapara Avenue, South C</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1289,17 +1289,17 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>'254 20 284 8000</t>
+          <t>'254 722 207 757</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>clerk@parliament.go.ke</t>
+          <t>info@kewi.or.ke</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>VANE</t>
+          <t>BABU</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr"/>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>KENYA WATER INSTITUTE</t>
+          <t>ATHI WATER WORKS DEVELOPMENT AGENCY</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Ole Shapara Avenue, South C</t>
+          <t>AWWDA Plaza (Athi Water Plaza), Muthaiga North Road, off Kiambu Road</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>'254 722 207 757</t>
+          <t>'254 715 688 272</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>info@kewi.or.ke</t>
+          <t>info@awwda.go.ke</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>ATHI WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>SPORTS KENYA</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>AWWDA Plaza (Athi Water Plaza), Muthaiga North Road, off Kiambu Road</t>
+          <t>Nyayo National Stadium, Uhuru Highway/Langata Rd/Aerodrome Rd Junction</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>'254 715 688 272</t>
+          <t>'254 20 239 2138</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>info@awwda.go.ke</t>
+          <t>info@sportskenya.org</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>BABU</t>
+          <t>GLORIA</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr"/>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>SPORTS KENYA</t>
+          <t>INTERGOVERNMENTAL RELATIONS TECHNICAL COMMITTEE</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Nyayo National Stadium, Uhuru Highway/Langata Rd/Aerodrome Rd Junction</t>
+          <t>Council of Governors / Delta Corner Annex, Waiyaki Way</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>'254 20 239 2138</t>
+          <t>'254 20 221 2136</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>info@sportskenya.org</t>
+          <t>info@igrtc.go.ke</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>INTERGOVERNMENTAL RELATIONS TECHNICAL COMMITTEE</t>
+          <t>SALARIES AND REMUNERATION COMMISSION</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Council of Governors / Delta Corner Annex, Waiyaki Way</t>
+          <t>Williamson House, 6th Floor, 4th Ngong Avenue, Upper Hill</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>'254 20 221 2136</t>
+          <t>'254 20 271 0081</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>info@igrtc.go.ke</t>
+          <t>info@src.go.ke</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>SALARIES AND REMUNERATION COMMISSION</t>
+          <t>OFFICE OF THE DATA PROTECTION COMMISSIONER</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Williamson House, 6th Floor, 4th Ngong Avenue, Upper Hill</t>
+          <t>Britam Towers, 12th Floor, Hospital Road, Upper Hill</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -1574,17 +1574,17 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>'254 20 271 0081</t>
+          <t>'254 703 025 888</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>info@src.go.ke</t>
+          <t>info@odpc.go.ke</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>GLORIA</t>
+          <t>CLYDE</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr"/>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>OFFICE OF THE DATA PROTECTION COMMISSIONER</t>
+          <t>OFFICE OF THE REGISTRAR OF POLITICAL PARTIES</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Britam Towers, 12th Floor, Hospital Road, Upper Hill</t>
+          <t>Lion(s) Place, 1st/2nd/4th Floors, Karuna Close, Waiyaki Way, Westlands</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>'254 703 025 888</t>
+          <t>'254 20 494 6000</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>info@odpc.go.ke</t>
+          <t>info@orpp.or.ke</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>OFFICE OF THE REGISTRAR OF POLITICAL PARTIES</t>
+          <t>TEACHERS SERVICE COMMISSION</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Lion(s) Place, 1st/2nd/4th Floors, Karuna Close, Waiyaki Way, Westlands</t>
+          <t>TSC House, Kilimanjaro Avenue, Upper Hill</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>'254 20 494 6000</t>
+          <t>'254 20 289 2000</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>info@orpp.or.ke</t>
+          <t>info@tsc.go.ke</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TEACHERS SERVICE COMMISSION</t>
+          <t>VETERINARY MEDICINES DIRECTORATE COUNCIL</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>TSC House, Kilimanjaro Avenue, Upper Hill</t>
+          <t>The Pest Control Plaza, Westlands</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>'254 20 289 2000</t>
+          <t>'254 722 762 679</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>info@tsc.go.ke</t>
+          <t>info@vmd.go.ke</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>CLYDE</t>
+          <t>JUDY</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr"/>
@@ -1782,39 +1782,35 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>VETERINARY MEDICINES DIRECTORATE COUNCIL</t>
+          <t>KERIO VALLEY DEVELOPMENT AUTHORITY</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>The Pest Control Plaza, Westlands</t>
+          <t>Oloo Street</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Eldoret</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Uasin Gishu</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>'254 722 762 679</t>
+          <t>'254 53 206 3361</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>info@vmd.go.ke</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>JUDY</t>
-        </is>
-      </c>
+          <t>info@kvda.go.ke</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr"/>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
@@ -1839,35 +1835,39 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>KERIO VALLEY DEVELOPMENT AUTHORITY</t>
+          <t>NATIONAL COUNCIL FOR PERSONS WITH DISABILITIES</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Oloo Street</t>
+          <t>Opposite ABC Place, Waiyaki Way</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Eldoret</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Uasin Gishu</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>'254 53 206 3361</t>
+          <t>'254 709 363 000</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>info@kvda.go.ke</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr"/>
+          <t>info@ncpwd.go.ke</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>JUDY</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr"/>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>NATIONAL COUNCIL FOR PERSONS WITH DISABILITIES</t>
+          <t>Public Benefit Organizations Regulatory Authority</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Opposite ABC Place, Waiyaki Way</t>
+          <t>Co-operative Bank House, 15th Floor, Haile Selassie Avenue</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -1912,17 +1912,17 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>'254 709 363 000</t>
+          <t>'254 20 221 4054</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>info@ncpwd.go.ke</t>
+          <t>info@pbo.go.ke</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>JUDY</t>
+          <t>JOB</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr"/>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Public Benefit Organizations Regulatory Authority</t>
+          <t>THE SENATE</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Co-operative Bank House, 15th Floor, Haile Selassie Avenue</t>
+          <t>Parliament Buildings, Parliament Road</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>'254 20 221 4054</t>
+          <t>'254 20 222 1291</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>info@pbo.go.ke</t>
+          <t>senate@parliament.go.ke</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -2006,39 +2006,15 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>THE SENATE</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Parliament Buildings, Parliament Road</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>'254 20 222 1291</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>senate@parliament.go.ke</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>JOB</t>
-        </is>
-      </c>
+          <t>STATE DEPARTMENT FOR HIGHER EDUCATION</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr"/>
+      <c r="D25" s="9" t="inlineStr"/>
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="9" t="inlineStr"/>
+      <c r="G25" s="9" t="inlineStr"/>
+      <c r="H25" s="10" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr"/>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
@@ -2638,39 +2614,15 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>KENYA NATIONAL HUMAN RIGHTS AND EQUALITY COMMISSION</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>CVS Plaza, Kasuku Road, off Lenana Road</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>'254 724 256 943</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>info@knchr.org</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>AMOS</t>
-        </is>
-      </c>
+          <t>STATE DEPARTMENT FOR TRADE</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr"/>
+      <c r="D37" s="9" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr"/>
+      <c r="F37" s="9" t="inlineStr"/>
+      <c r="G37" s="9" t="inlineStr"/>
+      <c r="H37" s="10" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
@@ -2695,12 +2647,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>RETIREMENT BENEFITS AUTHORITY</t>
+          <t>KENYA NATIONAL HUMAN RIGHTS AND EQUALITY COMMISSION</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Rahimtulla Tower, Upper Hill</t>
+          <t>CVS Plaza, Kasuku Road, off Lenana Road</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -2715,17 +2667,17 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>'254 20 280 9000</t>
+          <t>'254 724 256 943</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>info@rba.go.ke</t>
+          <t>info@knchr.org</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>CALEB</t>
+          <t>AMOS</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr"/>
@@ -2752,15 +2704,39 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>KITALE NATIONAL POLYTECHNIC</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr"/>
-      <c r="D39" s="9" t="inlineStr"/>
-      <c r="E39" s="9" t="inlineStr"/>
-      <c r="F39" s="9" t="inlineStr"/>
-      <c r="G39" s="9" t="inlineStr"/>
-      <c r="H39" s="10" t="inlineStr"/>
+          <t>RETIREMENT BENEFITS AUTHORITY</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Rahimtulla Tower, Upper Hill</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>'254 20 280 9000</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>info@rba.go.ke</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>CALEB</t>
+        </is>
+      </c>
       <c r="I39" s="4" t="inlineStr"/>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
@@ -2785,7 +2761,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>KENYA FILM COMMISSION</t>
+          <t>KITALE NATIONAL POLYTECHNIC</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr"/>
@@ -2818,31 +2794,15 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>KENYA ROADS BOARD</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Kenya Re Towers, 6th Floor</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
+          <t>NATIONAL GENDER AND EQUALITY COMMISSION</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr"/>
+      <c r="D41" s="9" t="inlineStr"/>
+      <c r="E41" s="9" t="inlineStr"/>
       <c r="F41" s="9" t="inlineStr"/>
       <c r="G41" s="9" t="inlineStr"/>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>CALEB</t>
-        </is>
-      </c>
+      <c r="H41" s="10" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr"/>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
@@ -2867,7 +2827,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR GENDER AFFAIRS &amp; AFFIRMATIVE ACTION</t>
+          <t>KENYA FILM COMMISSION</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr"/>
@@ -2900,12 +2860,12 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>PUBLIC SERVICE COMMISSION</t>
+          <t>KENYA ROADS BOARD</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Commission House, Harambee Avenue, Nairobi, Kenya.</t>
+          <t>Kenya Re Towers, 6th Floor</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -2918,19 +2878,11 @@
           <t>Nairobi</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>'254 20 2223901</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>psck@publicservice.go.ke</t>
-        </is>
-      </c>
+      <c r="F43" s="9" t="inlineStr"/>
+      <c r="G43" s="9" t="inlineStr"/>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>MUGAMBI</t>
+          <t>CALEB</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr"/>
@@ -2957,7 +2909,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>OFFICE OF THE AUDITOR-GENERAL</t>
+          <t>STATE DEPARTMENT FOR GENDER AFFAIRS &amp; AFFIRMATIVE ACTION</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr"/>
@@ -2990,12 +2942,12 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>ETHICS AND ANTI-CORRUPTION COMMISSION</t>
+          <t>PUBLIC SERVICE COMMISSION</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Jakaya Kikwete Road and Valley Road</t>
+          <t>Commission House, Harambee Avenue, Nairobi, Kenya.</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -3008,8 +2960,16 @@
           <t>Nairobi</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr"/>
-      <c r="G45" s="9" t="inlineStr"/>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>'254 20 2223901</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>psck@publicservice.go.ke</t>
+        </is>
+      </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
           <t>MUGAMBI</t>
@@ -3039,35 +2999,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>KENYA PLANT HEALTH INSPECTORATE SERVICES</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Ololua Ridge, Karen, Nairobi.</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>'254 709 891000</t>
-        </is>
-      </c>
+          <t>OFFICE OF THE AUDITOR-GENERAL</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr"/>
       <c r="G46" s="6" t="inlineStr"/>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>MUGAMBI</t>
-        </is>
-      </c>
+      <c r="H46" s="7" t="inlineStr"/>
       <c r="I46" s="4" t="inlineStr"/>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
@@ -3092,33 +3032,29 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>NATIONAL BIO-SAFETY AUTHORITY</t>
+          <t>ETHICS AND ANTI-CORRUPTION COMMISSION</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>NACOSTI Building, 2nd Floor, Upper Kabete, Off Waiyaki Way, Nairobi</t>
+          <t>Jakaya Kikwete Road and Valley Road</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>nairobi</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>nairobi</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>'254 713 854132</t>
-        </is>
-      </c>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr"/>
       <c r="G47" s="9" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>DUNCAN K</t>
+          <t>MUGAMBI</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr"/>
@@ -3145,15 +3081,35 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>EXECUTIVE OFFICE OF THE PRESIDENT</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr"/>
-      <c r="D48" s="6" t="inlineStr"/>
-      <c r="E48" s="6" t="inlineStr"/>
-      <c r="F48" s="6" t="inlineStr"/>
+          <t>KENYA PLANT HEALTH INSPECTORATE SERVICES</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Ololua Ridge, Karen, Nairobi.</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>'254 709 891000</t>
+        </is>
+      </c>
       <c r="G48" s="6" t="inlineStr"/>
-      <c r="H48" s="7" t="inlineStr"/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>MUGAMBI</t>
+        </is>
+      </c>
       <c r="I48" s="4" t="inlineStr"/>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>
@@ -3178,12 +3134,12 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>PEST CONTROL PRODUCTS BOARD</t>
+          <t>NATIONAL BIO-SAFETY AUTHORITY</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Loresho Ridge, Nairobi, Kenya</t>
+          <t>NACOSTI Building, 2nd Floor, Upper Kabete, Off Waiyaki Way, Nairobi</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -3198,7 +3154,7 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>'254 720 480 904</t>
+          <t>'254 713 854132</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr"/>
@@ -3231,7 +3187,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>MOI TEACHING AND REFERRAL HOSPITAL</t>
+          <t>EXECUTIVE OFFICE OF THE PRESIDENT</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr"/>
@@ -3264,15 +3220,35 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR PUBLIC SERVICE AND HUMAN CAPITAL DEVELOPMENT</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr"/>
-      <c r="D51" s="9" t="inlineStr"/>
-      <c r="E51" s="9" t="inlineStr"/>
-      <c r="F51" s="9" t="inlineStr"/>
+          <t>PEST CONTROL PRODUCTS BOARD</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Loresho Ridge, Nairobi, Kenya</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>nairobi</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>nairobi</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>'254 720 480 904</t>
+        </is>
+      </c>
       <c r="G51" s="9" t="inlineStr"/>
-      <c r="H51" s="10" t="inlineStr"/>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>DUNCAN K</t>
+        </is>
+      </c>
       <c r="I51" s="4" t="inlineStr"/>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n"/>
@@ -3297,7 +3273,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>KENYA NATIONAL TRADING CORPORATION</t>
+          <t>MOI TEACHING AND REFERRAL HOSPITAL</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr"/>
@@ -3330,7 +3306,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR INTERNAL SECURITY AND NATIONAL ADMINISTRATION</t>
+          <t>STATE DEPARTMENT FOR PUBLIC SERVICE AND HUMAN CAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr"/>
@@ -3363,19 +3339,11 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>NUMERICAL MACHINING COMPLEX</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Workshop Road, Industrial Area, Nairobi, Kenya</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>nairobi</t>
-        </is>
-      </c>
+          <t>KENYA NATIONAL TRADING CORPORATION</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr"/>
+      <c r="D54" s="6" t="inlineStr"/>
       <c r="E54" s="6" t="inlineStr"/>
       <c r="F54" s="6" t="inlineStr"/>
       <c r="G54" s="6" t="inlineStr"/>
@@ -3404,7 +3372,7 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>THE NATIONAL TREASURY</t>
+          <t>STATE DEPARTMENT FOR INTERNAL SECURITY AND NATIONAL ADMINISTRATION</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr"/>
@@ -3437,15 +3405,19 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>RIFT VALLEY TECHNICAL TRAINING INSTITUTE</t>
+          <t>NUMERICAL MACHINING COMPLEX</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Kaptagat Road, opposite KCC, Eldoret, Kenya</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr"/>
+          <t>Workshop Road, Industrial Area, Nairobi, Kenya</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>nairobi</t>
+        </is>
+      </c>
       <c r="E56" s="6" t="inlineStr"/>
       <c r="F56" s="6" t="inlineStr"/>
       <c r="G56" s="6" t="inlineStr"/>
@@ -3474,39 +3446,15 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR PUBLIC INVESTMENT &amp; ASSET MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>Treasury Building, Harambee Avenue</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>'254 20 225 2299</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>ps@treasury.go.ke</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>BRAISON</t>
-        </is>
-      </c>
+          <t>THE NATIONAL TREASURY</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr"/>
+      <c r="D57" s="9" t="inlineStr"/>
+      <c r="E57" s="9" t="inlineStr"/>
+      <c r="F57" s="9" t="inlineStr"/>
+      <c r="G57" s="9" t="inlineStr"/>
+      <c r="H57" s="10" t="inlineStr"/>
       <c r="I57" s="4" t="inlineStr"/>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
@@ -3531,39 +3479,19 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>POLICY HOLDERS COMPENSATION FUND</t>
+          <t>RIFT VALLEY TECHNICAL TRAINING INSTITUTE</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>KWFT Centre, 6th Floor, Masaba Road, Upper Hill</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>'254 20 490 6000</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>info@phcf.go.ke</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>AMOS</t>
-        </is>
-      </c>
+          <t>Kaptagat Road, opposite KCC, Eldoret, Kenya</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr"/>
+      <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr"/>
+      <c r="G58" s="6" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr"/>
       <c r="I58" s="4" t="inlineStr"/>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
@@ -3588,15 +3516,39 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>KENYA SPACE AGENCY</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr"/>
-      <c r="D59" s="9" t="inlineStr"/>
-      <c r="E59" s="9" t="inlineStr"/>
-      <c r="F59" s="9" t="inlineStr"/>
-      <c r="G59" s="9" t="inlineStr"/>
-      <c r="H59" s="10" t="inlineStr"/>
+          <t>STATE DEPARTMENT FOR PUBLIC INVESTMENT &amp; ASSET MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Treasury Building, Harambee Avenue</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>'254 20 225 2299</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>ps@treasury.go.ke</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>BRAISON</t>
+        </is>
+      </c>
       <c r="I59" s="4" t="inlineStr"/>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
@@ -3621,23 +3573,39 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>FINANCIAL INCLUSION FUND</t>
+          <t>POLICY HOLDERS COMPENSATION FUND</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>KIBT Complex, 3rd Floor, Ojijo Road, Nairobi.</t>
+          <t>KWFT Centre, 6th Floor, Masaba Road, Upper Hill</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>nairobi</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr"/>
-      <c r="F60" s="6" t="inlineStr"/>
-      <c r="G60" s="6" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr"/>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>'254 20 490 6000</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>info@phcf.go.ke</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>AMOS</t>
+        </is>
+      </c>
       <c r="I60" s="4" t="inlineStr"/>
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
@@ -3662,7 +3630,7 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>OFFICE OF THE PRIME CABINET SECRETARY</t>
+          <t>KENYA SPACE AGENCY</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr"/>
@@ -3695,12 +3663,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>KENYA INVESTMENT AUTHORITY</t>
+          <t>FINANCIAL INCLUSION FUND</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>UAP Old Mutual Towers, Upper Hill, 14th &amp; 15th Floors</t>
+          <t>KIBT Complex, 3rd Floor, Ojijo Road, Nairobi.</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -3711,16 +3679,8 @@
       <c r="E62" s="6" t="inlineStr"/>
       <c r="F62" s="6" t="inlineStr"/>
       <c r="G62" s="6" t="inlineStr"/>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>ESTHER</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>VISITED</t>
-        </is>
-      </c>
+      <c r="H62" s="7" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr"/>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
       <c r="L62" s="4" t="n"/>
@@ -3744,7 +3704,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>INDEPENDENT POLICING OVERSIGHT AUTHORITY</t>
+          <t>OFFICE OF THE PRIME CABINET SECRETARY</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr"/>
@@ -3777,16 +3737,32 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>THE NATIONAL HEROES COUNCIL</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr"/>
-      <c r="D64" s="6" t="inlineStr"/>
+          <t>KENYA INVESTMENT AUTHORITY</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>UAP Old Mutual Towers, Upper Hill, 14th &amp; 15th Floors</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>nairobi</t>
+        </is>
+      </c>
       <c r="E64" s="6" t="inlineStr"/>
       <c r="F64" s="6" t="inlineStr"/>
       <c r="G64" s="6" t="inlineStr"/>
-      <c r="H64" s="7" t="inlineStr"/>
-      <c r="I64" s="4" t="inlineStr"/>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>ESTHER</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>VISITED</t>
+        </is>
+      </c>
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
       <c r="L64" s="4" t="n"/>
@@ -3810,7 +3786,7 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR PARLIAMENTARY AFFAIRS</t>
+          <t>INDEPENDENT POLICING OVERSIGHT AUTHORITY</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr"/>
@@ -3843,7 +3819,7 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR MINING</t>
+          <t>THE NATIONAL HEROES COUNCIL</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr"/>
@@ -3876,19 +3852,11 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>RUIRU-JUJA WATER &amp; SEWERAGE COMPANY LTD</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>Off Thika Road, adjacent to Kenyatta University Ruiru Campus.</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>kiambu</t>
-        </is>
-      </c>
+          <t>STATE DEPARTMENT FOR PARLIAMENTARY AFFAIRS</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr"/>
+      <c r="D67" s="9" t="inlineStr"/>
       <c r="E67" s="9" t="inlineStr"/>
       <c r="F67" s="9" t="inlineStr"/>
       <c r="G67" s="9" t="inlineStr"/>
@@ -3917,7 +3885,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>KENYA CIVIL AVIATION AUTHORITY</t>
+          <t>STATE DEPARTMENT FOR MINING</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr"/>
@@ -3950,11 +3918,19 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>NATIONAL INDUSTRIAL TRAINING AUTHORITY</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr"/>
-      <c r="D69" s="9" t="inlineStr"/>
+          <t>RUIRU-JUJA WATER &amp; SEWERAGE COMPANY LTD</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>Off Thika Road, adjacent to Kenyatta University Ruiru Campus.</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>kiambu</t>
+        </is>
+      </c>
       <c r="E69" s="9" t="inlineStr"/>
       <c r="F69" s="9" t="inlineStr"/>
       <c r="G69" s="9" t="inlineStr"/>
@@ -3983,7 +3959,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR AVIATION AND AEROSPACE DEVELOPMENT</t>
+          <t>KENYA CIVIL AVIATION AUTHORITY</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr"/>
@@ -4016,10 +3992,14 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>NATIONAL POLICE SERVICE COMMISSION</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr"/>
+          <t>NATIONAL INDUSTRIAL TRAINING AUTHORITY</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Santander like many other banks is moving away</t>
+        </is>
+      </c>
       <c r="D71" s="9" t="inlineStr"/>
       <c r="E71" s="9" t="inlineStr"/>
       <c r="F71" s="9" t="inlineStr"/>
@@ -4049,7 +4029,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>NATIONAL SYNDEMIC DISEASES CONTROL COUNCIL</t>
+          <t>STATE DEPARTMENT FOR AVIATION AND AEROSPACE DEVELOPMENT</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr"/>
@@ -4082,20 +4062,12 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>KONZA TECHNOPOLIES DEVELOPMENT AUTHORITY</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>road</t>
-        </is>
-      </c>
+          <t>NATIONAL POLICE SERVICE COMMISSION</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr"/>
       <c r="D73" s="9" t="inlineStr"/>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
+      <c r="E73" s="9" t="inlineStr"/>
       <c r="F73" s="9" t="inlineStr"/>
       <c r="G73" s="9" t="inlineStr"/>
       <c r="H73" s="10" t="inlineStr"/>
@@ -4123,7 +4095,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>KENYA INSTITUTE OF SUPPLIES EXAMINATION BOARD</t>
+          <t>NATIONAL QUALITY CONTROL LABORATORY</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr"/>
@@ -4156,7 +4128,7 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR CABINET AFFAIRS</t>
+          <t>NATIONAL SYNDEMIC DISEASES CONTROL COUNCIL</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr"/>
@@ -4189,12 +4161,20 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>TEA BOARD OF KENYA</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr"/>
+          <t>KONZA TECHNOPOLIES DEVELOPMENT AUTHORITY</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
       <c r="D76" s="6" t="inlineStr"/>
-      <c r="E76" s="6" t="inlineStr"/>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
       <c r="F76" s="6" t="inlineStr"/>
       <c r="G76" s="6" t="inlineStr"/>
       <c r="H76" s="7" t="inlineStr"/>
@@ -4222,7 +4202,7 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>KENYA ACCREDITATION SERVICE</t>
+          <t>KENYA INSTITUTE OF SUPPLIES EXAMINATION BOARD</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr"/>
@@ -4255,39 +4235,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>TVET CURRICULUM DEVELOPMENT, ASSESSMENT AND CERTIFICATION COUNCIL</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>Absa Towers, 10th Floor, Loita Street</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>'254 700 015 440</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>cdacc.tvet@gmail.com</t>
-        </is>
-      </c>
-      <c r="H78" s="7" t="inlineStr">
-        <is>
-          <t>PETER</t>
-        </is>
-      </c>
+          <t>STATE DEPARTMENT FOR CABINET AFFAIRS</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr"/>
+      <c r="D78" s="6" t="inlineStr"/>
+      <c r="E78" s="6" t="inlineStr"/>
+      <c r="F78" s="6" t="inlineStr"/>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="4" t="inlineStr"/>
       <c r="J78" s="4" t="n"/>
       <c r="K78" s="4" t="n"/>
@@ -4312,7 +4268,7 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>COMMISSION ON REVENUE ALLOCATION</t>
+          <t>TEA BOARD OF KENYA</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr"/>
@@ -4345,7 +4301,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>NATIONAL TRANSPORT AND SAFETY AUTHORITY</t>
+          <t>KENYA ACCREDITATION SERVICE</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr"/>
@@ -4378,15 +4334,39 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>COMMISSION ON ADMINISTRATIVE JUSTICE</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="inlineStr"/>
-      <c r="D81" s="9" t="inlineStr"/>
-      <c r="E81" s="9" t="inlineStr"/>
-      <c r="F81" s="9" t="inlineStr"/>
-      <c r="G81" s="9" t="inlineStr"/>
-      <c r="H81" s="10" t="inlineStr"/>
+          <t>TVET CURRICULUM DEVELOPMENT, ASSESSMENT AND CERTIFICATION COUNCIL</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Absa Towers, 10th Floor, Loita Street</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>'254 700 015 440</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>cdacc.tvet@gmail.com</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>PETER</t>
+        </is>
+      </c>
       <c r="I81" s="4" t="inlineStr"/>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
@@ -4411,7 +4391,7 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>NEW KENYA PLANTERS CO-OPERATIVE UNION</t>
+          <t>NATIONAL TRANSPORT AND SAFETY AUTHORITY</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr"/>
@@ -4444,7 +4424,7 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>STATE DEPARTMMENT FOR SOCIAL PROTECTION AND SENIOR CITIZEN AFFAIRS</t>
+          <t>COMMISSION ON ADMINISTRATIVE JUSTICE</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr"/>
@@ -4477,7 +4457,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>KENYA SUGAR BOARD</t>
+          <t>NEW KENYA PLANTERS CO-OPERATIVE UNION</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr"/>
@@ -4510,7 +4490,7 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>TANA WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>STATE DEPARTMMENT FOR SOCIAL PROTECTION AND SENIOR CITIZEN AFFAIRS</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr"/>
@@ -4543,7 +4523,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR THE BLUE ECONOMY AND FISHERIES</t>
+          <t>KENYA SUGAR BOARD</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr"/>
@@ -4576,7 +4556,7 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>NATIONAL RESEARCH FUND</t>
+          <t>ANTI-DOPING AGENCY OF KENYA</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr"/>
@@ -4609,7 +4589,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>NAIROBI CENTRE FOR INTERNATIONAL ARBITRATION</t>
+          <t>STATE DEPARTMENT FOR THE BLUE ECONOMY AND FISHERIES</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr"/>
@@ -4642,7 +4622,7 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>HYDROLOGISTS REGISTRATION BOARD</t>
+          <t>STATE DEPARTMENT FOR INVESTMENTS PROMOTION</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr"/>
@@ -4675,7 +4655,7 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>KENYA COPYRIGHTS BOARD</t>
+          <t>NATIONAL RESEARCH FUND</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr"/>
@@ -4708,7 +4688,7 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>NATIONAL DEFENCE UNIVERSITY-KENYA</t>
+          <t>NAIROBI CENTRE FOR INTERNATIONAL ARBITRATION</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr"/>
@@ -4741,7 +4721,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>KENYA NATIONAL QUALIFICATIONS AUTHORITY</t>
+          <t>STATE DEPARTMENT FOR DIASPORA AFFAIRS</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr"/>
@@ -4774,7 +4754,7 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>NATIONAL COUNCIL FOR LAW REPORTING</t>
+          <t>HYDROLOGISTS REGISTRATION BOARD</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr"/>
@@ -4807,34 +4787,14 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>JOMO KENYATTA FOUNDATION</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>Denis Pritt Road (Head Office)</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>'254 723 286 99</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>info@jkf.co.ke</t>
-        </is>
-      </c>
+          <t>KENYA COPYRIGHTS BOARD</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr"/>
+      <c r="D94" s="6" t="inlineStr"/>
+      <c r="E94" s="6" t="inlineStr"/>
+      <c r="F94" s="6" t="inlineStr"/>
+      <c r="G94" s="6" t="inlineStr"/>
       <c r="H94" s="7" t="inlineStr"/>
       <c r="I94" s="4" t="inlineStr"/>
       <c r="J94" s="4" t="n"/>
@@ -4860,39 +4820,15 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>NUCLEAR POWER AND ENERGY AGENCY</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>Block C, Kawi House, off Red Cross Road, South C</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>'254 20 513 8300</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>info@nupea.go.ke</t>
-        </is>
-      </c>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>CHARLES</t>
-        </is>
-      </c>
+          <t>NATIONAL DEFENCE UNIVERSITY-KENYA</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr"/>
+      <c r="D95" s="6" t="inlineStr"/>
+      <c r="E95" s="6" t="inlineStr"/>
+      <c r="F95" s="6" t="inlineStr"/>
+      <c r="G95" s="6" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="4" t="inlineStr"/>
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="n"/>
@@ -4917,7 +4853,7 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>UGUNJA TECHNICAL AND VOCATIONAL COLLEGE</t>
+          <t>KENYA NATIONAL QUALIFICATIONS AUTHORITY</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr"/>
@@ -4950,7 +4886,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>KENYA ACADEMY OF SPORTS</t>
+          <t>NATIONAL COUNCIL FOR LAW REPORTING</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr"/>
@@ -4983,14 +4919,34 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>COMMUNICATIONS AUTHORITY OF KENYA</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr"/>
-      <c r="D98" s="6" t="inlineStr"/>
-      <c r="E98" s="6" t="inlineStr"/>
-      <c r="F98" s="6" t="inlineStr"/>
-      <c r="G98" s="6" t="inlineStr"/>
+          <t>JOMO KENYATTA FOUNDATION</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Denis Pritt Road (Head Office)</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>'254 723 286 99</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>info@jkf.co.ke</t>
+        </is>
+      </c>
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="4" t="inlineStr"/>
       <c r="J98" s="4" t="n"/>
@@ -5016,15 +4972,39 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>MEDIA COUNCIL OF KENYA</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr"/>
-      <c r="D99" s="6" t="inlineStr"/>
-      <c r="E99" s="6" t="inlineStr"/>
-      <c r="F99" s="6" t="inlineStr"/>
-      <c r="G99" s="6" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr"/>
+          <t>NUCLEAR POWER AND ENERGY AGENCY</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Block C, Kawi House, off Red Cross Road, South C</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>'254 20 513 8300</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>info@nupea.go.ke</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>CHARLES</t>
+        </is>
+      </c>
       <c r="I99" s="4" t="inlineStr"/>
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="4" t="n"/>
@@ -5049,14 +5029,10 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR CHILDREN SERVICES</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>statehouse</t>
-        </is>
-      </c>
+          <t>UGUNJA TECHNICAL AND VOCATIONAL COLLEGE</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr"/>
       <c r="D100" s="6" t="inlineStr"/>
       <c r="E100" s="6" t="inlineStr"/>
       <c r="F100" s="6" t="inlineStr"/>
@@ -5086,7 +5062,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>NATIONAL CANCER INSTITUTE OF KENYA</t>
+          <t>STATE DEPARTMENT FOR BASIC EDUCATION</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr"/>
@@ -5119,7 +5095,7 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>LAKE VICTORIA NORTH WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>KENYA ACADEMY OF SPORTS</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr"/>
@@ -5152,7 +5128,7 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>KENYA CULTURAL CENTRE</t>
+          <t>WILDLIFE CLUBS OF KENYA</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr"/>
@@ -5185,7 +5161,7 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>NORTHERN WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>COMMUNICATIONS AUTHORITY OF KENYA</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr"/>
@@ -5218,39 +5194,19 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>UNIVERSITIES FUND</t>
+          <t>STATE DEPARTMENT FOR CHILDREN SERVICES</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>5th Floor, Hazina Trade Centre, Monrovia Street, Nairobi</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>nairobi</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>nairobi</t>
-        </is>
-      </c>
-      <c r="F105" s="6" t="inlineStr">
-        <is>
-          <t>'254 746 737935</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>info@universitiesfund.go.ke</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>DUNCAN K</t>
-        </is>
-      </c>
+          <t>statehouse</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr"/>
+      <c r="E105" s="6" t="inlineStr"/>
+      <c r="F105" s="6" t="inlineStr"/>
+      <c r="G105" s="6" t="inlineStr"/>
+      <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="4" t="inlineStr"/>
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="4" t="n"/>
@@ -5275,39 +5231,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>UNCLAIMED FINANCIAL ASSETS AUTHORITY</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>Pacis Centre, 2nd Floor, Slip Road, off Waiyaki Way, Westlands</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>'254 20 402 3000</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>info@ufaa.go.ke</t>
-        </is>
-      </c>
-      <c r="H106" s="7" t="inlineStr">
-        <is>
-          <t>CALEB</t>
-        </is>
-      </c>
+          <t>NATIONAL CANCER INSTITUTE OF KENYA</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr"/>
+      <c r="D106" s="6" t="inlineStr"/>
+      <c r="E106" s="6" t="inlineStr"/>
+      <c r="F106" s="6" t="inlineStr"/>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="4" t="inlineStr"/>
       <c r="J106" s="4" t="n"/>
       <c r="K106" s="4" t="n"/>
@@ -5332,34 +5264,14 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>TOM MBOYA UNIVERSITY</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>Homa Bay–Mbita Road</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>Homa Bay</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>Homa Bay</t>
-        </is>
-      </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>'254 746 931 770</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>info@tmu.ac.ke</t>
-        </is>
-      </c>
+          <t>STATE DEPARTMENT FOR SPORTS</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr"/>
+      <c r="D107" s="6" t="inlineStr"/>
+      <c r="E107" s="6" t="inlineStr"/>
+      <c r="F107" s="6" t="inlineStr"/>
+      <c r="G107" s="6" t="inlineStr"/>
       <c r="H107" s="7" t="inlineStr"/>
       <c r="I107" s="4" t="inlineStr"/>
       <c r="J107" s="4" t="n"/>
@@ -5385,39 +5297,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>KENYA DAIRY BOARD</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>New Loresho Estate, Upper Kabete, off Waiyaki Way</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>Nairobi</t>
-        </is>
-      </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>'254 722 202 186</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>info@kdb.go.ke</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr">
-        <is>
-          <t>BABU</t>
-        </is>
-      </c>
+          <t>LAKE VICTORIA NORTH WATER WORKS DEVELOPMENT AGENCY</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr"/>
+      <c r="D108" s="6" t="inlineStr"/>
+      <c r="E108" s="6" t="inlineStr"/>
+      <c r="F108" s="6" t="inlineStr"/>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="4" t="inlineStr"/>
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="n"/>
@@ -5442,7 +5330,7 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>NAIROBI METROPOLITAN AREA TRANSPORT AUTHORITY</t>
+          <t>KENYA CULTURAL CENTRE</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr"/>
@@ -5470,15 +5358,21 @@
       <c r="Y109" s="4" t="n"/>
     </row>
     <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="15" t="n"/>
-      <c r="B110" s="16" t="n"/>
-      <c r="C110" s="16" t="n"/>
-      <c r="D110" s="16" t="n"/>
-      <c r="E110" s="16" t="n"/>
-      <c r="F110" s="16" t="n"/>
-      <c r="G110" s="16" t="n"/>
-      <c r="H110" s="17" t="n"/>
-      <c r="I110" s="17" t="n"/>
+      <c r="A110" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>NORTHERN WATER WORKS DEVELOPMENT AGENCY</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr"/>
+      <c r="D110" s="6" t="inlineStr"/>
+      <c r="E110" s="6" t="inlineStr"/>
+      <c r="F110" s="6" t="inlineStr"/>
+      <c r="G110" s="6" t="inlineStr"/>
+      <c r="H110" s="7" t="inlineStr"/>
+      <c r="I110" s="4" t="inlineStr"/>
       <c r="J110" s="4" t="n"/>
       <c r="K110" s="4" t="n"/>
       <c r="L110" s="4" t="n"/>
@@ -5497,15 +5391,45 @@
       <c r="Y110" s="4" t="n"/>
     </row>
     <row r="111" ht="15" customHeight="1">
-      <c r="A111" s="15" t="n"/>
-      <c r="B111" s="16" t="n"/>
-      <c r="C111" s="16" t="n"/>
-      <c r="D111" s="16" t="n"/>
-      <c r="E111" s="16" t="n"/>
-      <c r="F111" s="16" t="n"/>
-      <c r="G111" s="16" t="n"/>
-      <c r="H111" s="17" t="n"/>
-      <c r="I111" s="17" t="n"/>
+      <c r="A111" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>UNIVERSITIES FUND</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>5th Floor, Hazina Trade Centre, Monrovia Street, Nairobi</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>nairobi</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>nairobi</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>'254 746 737935</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>info@universitiesfund.go.ke</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>DUNCAN K</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr"/>
       <c r="J111" s="4" t="n"/>
       <c r="K111" s="4" t="n"/>
       <c r="L111" s="4" t="n"/>
@@ -5524,15 +5448,21 @@
       <c r="Y111" s="4" t="n"/>
     </row>
     <row r="112" ht="15" customHeight="1">
-      <c r="A112" s="15" t="n"/>
-      <c r="B112" s="16" t="n"/>
-      <c r="C112" s="16" t="n"/>
-      <c r="D112" s="16" t="n"/>
-      <c r="E112" s="16" t="n"/>
-      <c r="F112" s="16" t="n"/>
-      <c r="G112" s="16" t="n"/>
-      <c r="H112" s="17" t="n"/>
-      <c r="I112" s="17" t="n"/>
+      <c r="A112" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>TANA AND ATHI RIVERS DEVELOPMENT AUTHORITY</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr"/>
+      <c r="D112" s="6" t="inlineStr"/>
+      <c r="E112" s="6" t="inlineStr"/>
+      <c r="F112" s="6" t="inlineStr"/>
+      <c r="G112" s="6" t="inlineStr"/>
+      <c r="H112" s="7" t="inlineStr"/>
+      <c r="I112" s="4" t="inlineStr"/>
       <c r="J112" s="4" t="n"/>
       <c r="K112" s="4" t="n"/>
       <c r="L112" s="4" t="n"/>
@@ -5551,15 +5481,41 @@
       <c r="Y112" s="4" t="n"/>
     </row>
     <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="15" t="n"/>
-      <c r="B113" s="16" t="n"/>
-      <c r="C113" s="16" t="n"/>
-      <c r="D113" s="16" t="n"/>
-      <c r="E113" s="16" t="n"/>
-      <c r="F113" s="16" t="n"/>
-      <c r="G113" s="16" t="n"/>
-      <c r="H113" s="17" t="n"/>
-      <c r="I113" s="17" t="n"/>
+      <c r="A113" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>TOM MBOYA UNIVERSITY</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>Homa Bay–Mbita Road</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>Homa Bay</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>Homa Bay</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>'254 746 931 770</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>info@tmu.ac.ke</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="inlineStr"/>
+      <c r="I113" s="4" t="inlineStr"/>
       <c r="J113" s="4" t="n"/>
       <c r="K113" s="4" t="n"/>
       <c r="L113" s="4" t="n"/>
@@ -5578,15 +5534,21 @@
       <c r="Y113" s="4" t="n"/>
     </row>
     <row r="114" ht="15" customHeight="1">
-      <c r="A114" s="15" t="n"/>
-      <c r="B114" s="16" t="n"/>
-      <c r="C114" s="16" t="n"/>
-      <c r="D114" s="16" t="n"/>
-      <c r="E114" s="16" t="n"/>
-      <c r="F114" s="16" t="n"/>
-      <c r="G114" s="16" t="n"/>
-      <c r="H114" s="17" t="n"/>
-      <c r="I114" s="17" t="n"/>
+      <c r="A114" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>CHUKA UNIVERSITY</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr"/>
+      <c r="D114" s="6" t="inlineStr"/>
+      <c r="E114" s="6" t="inlineStr"/>
+      <c r="F114" s="6" t="inlineStr"/>
+      <c r="G114" s="6" t="inlineStr"/>
+      <c r="H114" s="7" t="inlineStr"/>
+      <c r="I114" s="4" t="inlineStr"/>
       <c r="J114" s="4" t="n"/>
       <c r="K114" s="4" t="n"/>
       <c r="L114" s="4" t="n"/>
@@ -5605,15 +5567,45 @@
       <c r="Y114" s="4" t="n"/>
     </row>
     <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="15" t="n"/>
-      <c r="B115" s="16" t="n"/>
-      <c r="C115" s="16" t="n"/>
-      <c r="D115" s="16" t="n"/>
-      <c r="E115" s="16" t="n"/>
-      <c r="F115" s="16" t="n"/>
-      <c r="G115" s="16" t="n"/>
-      <c r="H115" s="17" t="n"/>
-      <c r="I115" s="17" t="n"/>
+      <c r="A115" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>KENYA DAIRY BOARD</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>New Loresho Estate, Upper Kabete, off Waiyaki Way</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>'254 722 202 186</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>info@kdb.go.ke</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="inlineStr">
+        <is>
+          <t>BABU</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr"/>
       <c r="J115" s="4" t="n"/>
       <c r="K115" s="4" t="n"/>
       <c r="L115" s="4" t="n"/>
@@ -5632,15 +5624,21 @@
       <c r="Y115" s="4" t="n"/>
     </row>
     <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="15" t="n"/>
-      <c r="B116" s="16" t="n"/>
-      <c r="C116" s="16" t="n"/>
-      <c r="D116" s="16" t="n"/>
-      <c r="E116" s="16" t="n"/>
-      <c r="F116" s="16" t="n"/>
-      <c r="G116" s="16" t="n"/>
-      <c r="H116" s="17" t="n"/>
-      <c r="I116" s="17" t="n"/>
+      <c r="A116" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>STATE DEPARTMENT FOR SCIENCE, RESEARCH AND INNOVATION</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr"/>
+      <c r="D116" s="6" t="inlineStr"/>
+      <c r="E116" s="6" t="inlineStr"/>
+      <c r="F116" s="6" t="inlineStr"/>
+      <c r="G116" s="6" t="inlineStr"/>
+      <c r="H116" s="7" t="inlineStr"/>
+      <c r="I116" s="4" t="inlineStr"/>
       <c r="J116" s="4" t="n"/>
       <c r="K116" s="4" t="n"/>
       <c r="L116" s="4" t="n"/>
@@ -5659,15 +5657,21 @@
       <c r="Y116" s="4" t="n"/>
     </row>
     <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="15" t="n"/>
-      <c r="B117" s="16" t="n"/>
-      <c r="C117" s="16" t="n"/>
-      <c r="D117" s="16" t="n"/>
-      <c r="E117" s="16" t="n"/>
-      <c r="F117" s="16" t="n"/>
-      <c r="G117" s="16" t="n"/>
-      <c r="H117" s="17" t="n"/>
-      <c r="I117" s="17" t="n"/>
+      <c r="A117" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>TANA WATER WORKS DEVELOPMENT AGENCY</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr"/>
+      <c r="D117" s="6" t="inlineStr"/>
+      <c r="E117" s="6" t="inlineStr"/>
+      <c r="F117" s="6" t="inlineStr"/>
+      <c r="G117" s="6" t="inlineStr"/>
+      <c r="H117" s="7" t="inlineStr"/>
+      <c r="I117" s="4" t="inlineStr"/>
       <c r="J117" s="4" t="n"/>
       <c r="K117" s="4" t="n"/>
       <c r="L117" s="4" t="n"/>
@@ -5686,15 +5690,21 @@
       <c r="Y117" s="4" t="n"/>
     </row>
     <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="15" t="n"/>
-      <c r="B118" s="16" t="n"/>
-      <c r="C118" s="16" t="n"/>
-      <c r="D118" s="16" t="n"/>
-      <c r="E118" s="16" t="n"/>
-      <c r="F118" s="16" t="n"/>
-      <c r="G118" s="16" t="n"/>
-      <c r="H118" s="17" t="n"/>
-      <c r="I118" s="17" t="n"/>
+      <c r="A118" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>NAIROBI METROPOLITAN AREA TRANSPORT AUTHORITY</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr"/>
+      <c r="D118" s="6" t="inlineStr"/>
+      <c r="E118" s="6" t="inlineStr"/>
+      <c r="F118" s="6" t="inlineStr"/>
+      <c r="G118" s="6" t="inlineStr"/>
+      <c r="H118" s="7" t="inlineStr"/>
+      <c r="I118" s="4" t="inlineStr"/>
       <c r="J118" s="4" t="n"/>
       <c r="K118" s="4" t="n"/>
       <c r="L118" s="4" t="n"/>
@@ -5713,15 +5723,45 @@
       <c r="Y118" s="4" t="n"/>
     </row>
     <row r="119" ht="15" customHeight="1">
-      <c r="A119" s="15" t="n"/>
-      <c r="B119" s="16" t="n"/>
-      <c r="C119" s="16" t="n"/>
-      <c r="D119" s="16" t="n"/>
-      <c r="E119" s="16" t="n"/>
-      <c r="F119" s="16" t="n"/>
-      <c r="G119" s="16" t="n"/>
-      <c r="H119" s="17" t="n"/>
-      <c r="I119" s="17" t="n"/>
+      <c r="A119" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>UNCLAIMED FINANCIAL ASSETS AUTHORITY</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>Pacis Centre, 2nd Floor, Slip Road, off Waiyaki Way, Westlands</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>'254 20 402 3000</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>info@ufaa.go.ke</t>
+        </is>
+      </c>
+      <c r="H119" s="7" t="inlineStr">
+        <is>
+          <t>CALEB</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr"/>
       <c r="J119" s="4" t="n"/>
       <c r="K119" s="4" t="n"/>
       <c r="L119" s="4" t="n"/>
@@ -5740,15 +5780,45 @@
       <c r="Y119" s="4" t="n"/>
     </row>
     <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="15" t="n"/>
-      <c r="B120" s="16" t="n"/>
-      <c r="C120" s="16" t="n"/>
-      <c r="D120" s="16" t="n"/>
-      <c r="E120" s="16" t="n"/>
-      <c r="F120" s="16" t="n"/>
-      <c r="G120" s="16" t="n"/>
-      <c r="H120" s="17" t="n"/>
-      <c r="I120" s="17" t="n"/>
+      <c r="A120" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>COUNCIL FOR LEGAL EDUCATION</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>Karen Office Park, Karen</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>'254 20 266 5440</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>info@cle.or.ke</t>
+        </is>
+      </c>
+      <c r="H120" s="7" t="inlineStr">
+        <is>
+          <t>VANE</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr"/>
       <c r="J120" s="4" t="n"/>
       <c r="K120" s="4" t="n"/>
       <c r="L120" s="4" t="n"/>
@@ -5767,15 +5837,21 @@
       <c r="Y120" s="4" t="n"/>
     </row>
     <row r="121" ht="15" customHeight="1">
-      <c r="A121" s="15" t="n"/>
-      <c r="B121" s="16" t="n"/>
-      <c r="C121" s="16" t="n"/>
-      <c r="D121" s="16" t="n"/>
-      <c r="E121" s="16" t="n"/>
-      <c r="F121" s="16" t="n"/>
-      <c r="G121" s="16" t="n"/>
-      <c r="H121" s="17" t="n"/>
-      <c r="I121" s="17" t="n"/>
+      <c r="A121" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>COMMISSION ON REVENUE ALLOCATION</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr"/>
+      <c r="D121" s="6" t="inlineStr"/>
+      <c r="E121" s="6" t="inlineStr"/>
+      <c r="F121" s="6" t="inlineStr"/>
+      <c r="G121" s="6" t="inlineStr"/>
+      <c r="H121" s="7" t="inlineStr"/>
+      <c r="I121" s="4" t="inlineStr"/>
       <c r="J121" s="4" t="n"/>
       <c r="K121" s="4" t="n"/>
       <c r="L121" s="4" t="n"/>
@@ -5794,15 +5870,21 @@
       <c r="Y121" s="4" t="n"/>
     </row>
     <row r="122" ht="15" customHeight="1">
-      <c r="A122" s="15" t="n"/>
-      <c r="B122" s="16" t="n"/>
-      <c r="C122" s="16" t="n"/>
-      <c r="D122" s="16" t="n"/>
-      <c r="E122" s="16" t="n"/>
-      <c r="F122" s="16" t="n"/>
-      <c r="G122" s="16" t="n"/>
-      <c r="H122" s="17" t="n"/>
-      <c r="I122" s="17" t="n"/>
+      <c r="A122" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>KENYA SCHOOL OF LAW</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr"/>
+      <c r="D122" s="6" t="inlineStr"/>
+      <c r="E122" s="6" t="inlineStr"/>
+      <c r="F122" s="6" t="inlineStr"/>
+      <c r="G122" s="6" t="inlineStr"/>
+      <c r="H122" s="7" t="inlineStr"/>
+      <c r="I122" s="4" t="inlineStr"/>
       <c r="J122" s="4" t="n"/>
       <c r="K122" s="4" t="n"/>
       <c r="L122" s="4" t="n"/>
@@ -5821,15 +5903,21 @@
       <c r="Y122" s="4" t="n"/>
     </row>
     <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="17" t="n"/>
-      <c r="B123" s="17" t="n"/>
-      <c r="C123" s="17" t="n"/>
-      <c r="D123" s="17" t="n"/>
-      <c r="E123" s="17" t="n"/>
-      <c r="F123" s="17" t="n"/>
-      <c r="G123" s="17" t="n"/>
-      <c r="H123" s="17" t="n"/>
-      <c r="I123" s="17" t="n"/>
+      <c r="A123" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>MEDIA COUNCIL OF KENYA</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr"/>
+      <c r="D123" s="6" t="inlineStr"/>
+      <c r="E123" s="6" t="inlineStr"/>
+      <c r="F123" s="6" t="inlineStr"/>
+      <c r="G123" s="6" t="inlineStr"/>
+      <c r="H123" s="7" t="inlineStr"/>
+      <c r="I123" s="4" t="inlineStr"/>
       <c r="J123" s="4" t="n"/>
       <c r="K123" s="4" t="n"/>
       <c r="L123" s="4" t="n"/>
@@ -29649,7 +29737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29919,21 +30007,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>COUNCIL FOR LEGAL EDUCATION</t>
+          <t>NATIONAL DROUGHT MANAGEMENT AUTHORITY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CLE/799/APP/2026-27/2</t>
+          <t>NDMA/1080/APP/2026-27/3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/30228/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/30248/1/</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>30228</v>
+        <v>30248</v>
       </c>
     </row>
     <row r="11">
@@ -29947,21 +30035,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NATIONAL DROUGHT MANAGEMENT AUTHORITY</t>
+          <t>PARLIAMENTARY SERVICE COMMISSION</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NDMA/1080/APP/2026-27/3</t>
+          <t>PARLSC/1145/APP/2026-27/2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/30248/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/30332/1/</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>30248</v>
+        <v>30332</v>
       </c>
     </row>
     <row r="12">
@@ -29975,21 +30063,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PARLIAMENTARY SERVICE COMMISSION</t>
+          <t>KENYA WATER INSTITUTE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PARLSC/1145/APP/2026-27/2</t>
+          <t>KEWI/708/APP/2026-27/5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/30332/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/30459/1/</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30332</v>
+        <v>30459</v>
       </c>
     </row>
     <row r="13">
@@ -30003,21 +30091,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KENYA WATER INSTITUTE</t>
+          <t>ATHI WATER WORKS DEVELOPMENT AGENCY</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KEWI/708/APP/2026-27/5</t>
+          <t>AWWDA/704/APP/2026-27/2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/30459/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/30470/1/</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>30459</v>
+        <v>30470</v>
       </c>
     </row>
     <row r="14">
@@ -30031,21 +30119,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ATHI WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>SPORTS KENYA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AWWDA/704/APP/2026-27/2</t>
+          <t>SK/1036/APP/2026-27/13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/30470/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/30632/1/</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>30470</v>
+        <v>30632</v>
       </c>
     </row>
     <row r="15">
@@ -30059,21 +30147,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SPORTS KENYA</t>
+          <t>INTERGOVERNMENTAL RELATIONS TECHNICAL COMMITTEE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SK/1036/APP/2026-27/13</t>
+          <t>IGRTC/1223/APP/2026-27/4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/30632/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/30645/1/</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>30632</v>
+        <v>30645</v>
       </c>
     </row>
     <row r="16">
@@ -30087,21 +30175,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INTERGOVERNMENTAL RELATIONS TECHNICAL COMMITTEE</t>
+          <t>SALARIES AND REMUNERATION COMMISSION</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IGRTC/1223/APP/2026-27/4</t>
+          <t>SRC/723/APP/2026-27/4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/30645/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/30685/1/</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>30645</v>
+        <v>30685</v>
       </c>
     </row>
     <row r="17">
@@ -30115,21 +30203,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SALARIES AND REMUNERATION COMMISSION</t>
+          <t>OFFICE OF THE DATA PROTECTION COMMISSIONER</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SRC/723/APP/2026-27/4</t>
+          <t>ODPC/1154/APP/2026-27/2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/30685/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/30758/1/</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>30685</v>
+        <v>30758</v>
       </c>
     </row>
     <row r="18">
@@ -30143,21 +30231,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OFFICE OF THE DATA PROTECTION COMMISSIONER</t>
+          <t>OFFICE OF THE REGISTRAR OF POLITICAL PARTIES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ODPC/1154/APP/2026-27/2</t>
+          <t>ORPP/1144/APP/2026-27/8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/30758/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/30810/1/</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>30758</v>
+        <v>30810</v>
       </c>
     </row>
     <row r="19">
@@ -30171,21 +30259,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OFFICE OF THE REGISTRAR OF POLITICAL PARTIES</t>
+          <t>TEACHERS SERVICE COMMISSION</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ORPP/1144/APP/2026-27/8</t>
+          <t>TSC/722/APP/2026-27/3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/30810/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/30874/1/</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>30810</v>
+        <v>30874</v>
       </c>
     </row>
     <row r="20">
@@ -30199,21 +30287,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TEACHERS SERVICE COMMISSION</t>
+          <t>VETERINARY MEDICINES DIRECTORATE COUNCIL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TSC/722/APP/2026-27/3</t>
+          <t>VMD/769/APP/2026-27/5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/30874/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/30881/1/</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>30874</v>
+        <v>30881</v>
       </c>
     </row>
     <row r="21">
@@ -30227,21 +30315,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VETERINARY MEDICINES DIRECTORATE COUNCIL</t>
+          <t>KERIO VALLEY DEVELOPMENT AUTHORITY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VMD/769/APP/2026-27/5</t>
+          <t>KVDA/1078/APP/2026-27/3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/30881/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/31149/1/</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>30881</v>
+        <v>31149</v>
       </c>
     </row>
     <row r="22">
@@ -30255,21 +30343,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KERIO VALLEY DEVELOPMENT AUTHORITY</t>
+          <t>NATIONAL COUNCIL FOR PERSONS WITH DISABILITIES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KVDA/1078/APP/2026-27/3</t>
+          <t>NCPWD/1100/APP/2026-27/4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/31149/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/31266/1/</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>31149</v>
+        <v>31266</v>
       </c>
     </row>
     <row r="23">
@@ -30283,21 +30371,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NATIONAL COUNCIL FOR PERSONS WITH DISABILITIES</t>
+          <t>Public Benefit Organizations Regulatory Authority</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NCPWD/1100/APP/2026-27/4</t>
+          <t>NGOCB/910/APP/2026-27/10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/31266/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/31382/1/</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>31266</v>
+        <v>31382</v>
       </c>
     </row>
     <row r="24">
@@ -30311,21 +30399,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Public Benefit Organizations Regulatory Authority</t>
+          <t>THE SENATE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NGOCB/910/APP/2026-27/10</t>
+          <t>SEN/1146/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/31382/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/31452/1/</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>31382</v>
+        <v>31452</v>
       </c>
     </row>
     <row r="25">
@@ -30339,21 +30427,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>THE SENATE</t>
+          <t>STATE DEPARTMENT FOR HIGHER EDUCATION</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SEN/1146/APP/2026-27/1</t>
+          <t>SDHE/809/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/31452/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/31485/1/</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>31452</v>
+        <v>31485</v>
       </c>
     </row>
     <row r="26">
@@ -30675,21 +30763,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KENYA NATIONAL HUMAN RIGHTS AND EQUALITY COMMISSION</t>
+          <t>STATE DEPARTMENT FOR TRADE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KNHREC/716/APP/2026-27/1</t>
+          <t>SDTRADE/1006/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/32690/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/32552/1/</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>32690</v>
+        <v>32552</v>
       </c>
     </row>
     <row r="38">
@@ -30703,21 +30791,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RETIREMENT BENEFITS AUTHORITY</t>
+          <t>KENYA NATIONAL HUMAN RIGHTS AND EQUALITY COMMISSION</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>RBA/937/APP/2026-27/1</t>
+          <t>KNHREC/716/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/32738/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/32690/1/</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>32738</v>
+        <v>32690</v>
       </c>
     </row>
     <row r="39">
@@ -30731,21 +30819,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KITALE NATIONAL POLYTECHNIC</t>
+          <t>RETIREMENT BENEFITS AUTHORITY</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TKNP/867/APP/2026-27/1</t>
+          <t>RBA/937/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/32757/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/32738/1/</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>32757</v>
+        <v>32738</v>
       </c>
     </row>
     <row r="40">
@@ -30759,21 +30847,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KENYA FILM COMMISSION</t>
+          <t>KITALE NATIONAL POLYTECHNIC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KFC/1028/APP/2026-27/1</t>
+          <t>TKNP/867/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/32890/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/32757/1/</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>32890</v>
+        <v>32757</v>
       </c>
     </row>
     <row r="41">
@@ -30787,21 +30875,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KENYA ROADS BOARD</t>
+          <t>NATIONAL GENDER AND EQUALITY COMMISSION</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KRB/928/APP/2026-27/1</t>
+          <t>NGEC/730/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33104/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/32829/1/</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>33104</v>
+        <v>32829</v>
       </c>
     </row>
     <row r="42">
@@ -30815,21 +30903,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR GENDER AFFAIRS &amp; AFFIRMATIVE ACTION</t>
+          <t>KENYA FILM COMMISSION</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SDGAA/973/APP/2026-27/1</t>
+          <t>KFC/1028/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33158/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/32890/1/</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>33158</v>
+        <v>32890</v>
       </c>
     </row>
     <row r="43">
@@ -30843,21 +30931,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PUBLIC SERVICE COMMISSION</t>
+          <t>KENYA ROADS BOARD</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PSC/721/APP/2026-27/1</t>
+          <t>KRB/928/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33206/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33104/1/</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>33206</v>
+        <v>33104</v>
       </c>
     </row>
     <row r="44">
@@ -30871,21 +30959,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OFFICE OF THE AUDITOR-GENERAL</t>
+          <t>STATE DEPARTMENT FOR GENDER AFFAIRS &amp; AFFIRMATIVE ACTION</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OAG/7/APP/2026-27/1</t>
+          <t>SDGAA/973/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33228/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33158/1/</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>33228</v>
+        <v>33158</v>
       </c>
     </row>
     <row r="45">
@@ -30899,21 +30987,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ETHICS AND ANTI-CORRUPTION COMMISSION</t>
+          <t>PUBLIC SERVICE COMMISSION</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EACC/183/APP/2026-27/1</t>
+          <t>PSC/721/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33308/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33206/1/</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>33308</v>
+        <v>33206</v>
       </c>
     </row>
     <row r="46">
@@ -30927,21 +31015,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KENYA PLANT HEALTH INSPECTORATE SERVICES</t>
+          <t>OFFICE OF THE AUDITOR-GENERAL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KEPHIS/742/APP/2026-27/1</t>
+          <t>OAG/7/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33323/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33228/1/</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>33323</v>
+        <v>33228</v>
       </c>
     </row>
     <row r="47">
@@ -30955,21 +31043,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NATIONAL BIO-SAFETY AUTHORITY</t>
+          <t>ETHICS AND ANTI-CORRUPTION COMMISSION</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NBA/753/APP/2026-27/1</t>
+          <t>EACC/183/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33450/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33308/1/</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>33450</v>
+        <v>33308</v>
       </c>
     </row>
     <row r="48">
@@ -30983,21 +31071,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EXECUTIVE OFFICE OF THE PRESIDENT</t>
+          <t>KENYA PLANT HEALTH INSPECTORATE SERVICES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EOOP/1827/APP/2026-27/1</t>
+          <t>KEPHIS/742/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33520/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33323/1/</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>33520</v>
+        <v>33323</v>
       </c>
     </row>
     <row r="49">
@@ -31011,21 +31099,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PEST CONTROL PRODUCTS BOARD</t>
+          <t>NATIONAL BIO-SAFETY AUTHORITY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PCPB/754/APP/2026-27/1</t>
+          <t>NBA/753/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33587/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33450/1/</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>33587</v>
+        <v>33450</v>
       </c>
     </row>
     <row r="50">
@@ -31039,21 +31127,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MOI TEACHING AND REFERRAL HOSPITAL</t>
+          <t>EXECUTIVE OFFICE OF THE PRESIDENT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MTRH/58/APP/2026-27/1</t>
+          <t>EOOP/1827/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33600/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33520/1/</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>33600</v>
+        <v>33520</v>
       </c>
     </row>
     <row r="51">
@@ -31067,21 +31155,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR PUBLIC SERVICE AND HUMAN CAPITAL DEVELOPMENT</t>
+          <t>PEST CONTROL PRODUCTS BOARD</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SDPSHCD/55/APP/2026-27/1</t>
+          <t>PCPB/754/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33631/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33587/1/</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>33631</v>
+        <v>33587</v>
       </c>
     </row>
     <row r="52">
@@ -31095,21 +31183,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KENYA NATIONAL TRADING CORPORATION</t>
+          <t>MOI TEACHING AND REFERRAL HOSPITAL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KNTC/1102/APP/2026-27/1</t>
+          <t>MTRH/58/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33752/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33600/1/</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>33752</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="53">
@@ -31123,21 +31211,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR INTERNAL SECURITY AND NATIONAL ADMINISTRATION</t>
+          <t>STATE DEPARTMENT FOR PUBLIC SERVICE AND HUMAN CAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SDISNA/749/APP/2026-27/1</t>
+          <t>SDPSHCD/55/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33846/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33631/1/</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>33846</v>
+        <v>33631</v>
       </c>
     </row>
     <row r="54">
@@ -31151,21 +31239,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NUMERICAL MACHINING COMPLEX</t>
+          <t>KENYA NATIONAL TRADING CORPORATION</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NMC/1037/APP/2026-27/1</t>
+          <t>KNTC/1102/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33859/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33752/1/</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>33859</v>
+        <v>33752</v>
       </c>
     </row>
     <row r="55">
@@ -31179,21 +31267,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>THE NATIONAL TREASURY</t>
+          <t>STATE DEPARTMENT FOR INTERNAL SECURITY AND NATIONAL ADMINISTRATION</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TNT/14/APP/2026-27/1</t>
+          <t>SDISNA/749/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33893/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33846/1/</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>33893</v>
+        <v>33846</v>
       </c>
     </row>
     <row r="56">
@@ -31207,21 +31295,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RIFT VALLEY TECHNICAL TRAINING INSTITUTE</t>
+          <t>NUMERICAL MACHINING COMPLEX</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>RVTTI/1893/APP/2026-27/1</t>
+          <t>NMC/1037/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33947/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33859/1/</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>33947</v>
+        <v>33859</v>
       </c>
     </row>
     <row r="57">
@@ -31235,21 +31323,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR PUBLIC INVESTMENT &amp; ASSET MANAGEMENT</t>
+          <t>THE NATIONAL TREASURY</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SDPIAM/1121/APP/2026-27/2</t>
+          <t>TNT/14/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33955/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33893/1/</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>33955</v>
+        <v>33893</v>
       </c>
     </row>
     <row r="58">
@@ -31263,21 +31351,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>POLICY HOLDERS COMPENSATION FUND</t>
+          <t>RIFT VALLEY TECHNICAL TRAINING INSTITUTE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PCF/946/APP/2026-27/2</t>
+          <t>RVTTI/1893/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33992/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33947/1/</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>33992</v>
+        <v>33947</v>
       </c>
     </row>
     <row r="59">
@@ -31291,21 +31379,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KENYA SPACE AGENCY</t>
+          <t>STATE DEPARTMENT FOR PUBLIC INVESTMENT &amp; ASSET MANAGEMENT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KSA/1012/APP/2026-27/1</t>
+          <t>SDPIAM/1121/APP/2026-27/2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/33995/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33955/1/</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>33995</v>
+        <v>33955</v>
       </c>
     </row>
     <row r="60">
@@ -31319,21 +31407,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FINANCIAL INCLUSION FUND</t>
+          <t>POLICY HOLDERS COMPENSATION FUND</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FIF/1204/APP/2026-27/1</t>
+          <t>PCF/946/APP/2026-27/2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/34007/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33992/1/</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>34007</v>
+        <v>33992</v>
       </c>
     </row>
     <row r="61">
@@ -31347,21 +31435,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OFFICE OF THE PRIME CABINET SECRETARY</t>
+          <t>KENYA SPACE AGENCY</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OPCS/744/APP/2026-27/1</t>
+          <t>KSA/1012/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/34071/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/33995/1/</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>34071</v>
+        <v>33995</v>
       </c>
     </row>
     <row r="62">
@@ -31375,21 +31463,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KENYA INVESTMENT AUTHORITY</t>
+          <t>FINANCIAL INCLUSION FUND</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KENINVEST/1090/APP/2026-27/1</t>
+          <t>FIF/1204/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/34080/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/34007/1/</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>34080</v>
+        <v>34007</v>
       </c>
     </row>
     <row r="63">
@@ -31403,21 +31491,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>INDEPENDENT POLICING OVERSIGHT AUTHORITY</t>
+          <t>OFFICE OF THE PRIME CABINET SECRETARY</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>IP0A/2063/APP/2026-27/1</t>
+          <t>OPCS/744/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/34166/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/34071/1/</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>34166</v>
+        <v>34071</v>
       </c>
     </row>
     <row r="64">
@@ -31431,21 +31519,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>THE NATIONAL HEROES COUNCIL</t>
+          <t>KENYA INVESTMENT AUTHORITY</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8516/1203/APP/2026-27/1</t>
+          <t>KENINVEST/1090/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/34233/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/34080/1/</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>34233</v>
+        <v>34080</v>
       </c>
     </row>
     <row r="65">
@@ -31459,21 +31547,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR PARLIAMENTARY AFFAIRS</t>
+          <t>INDEPENDENT POLICING OVERSIGHT AUTHORITY</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SDPA/747/APP/2026-27/1</t>
+          <t>IP0A/2063/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/34307/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/34166/1/</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>34307</v>
+        <v>34166</v>
       </c>
     </row>
     <row r="66">
@@ -31487,21 +31575,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR MINING</t>
+          <t>THE NATIONAL HEROES COUNCIL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SDM/794/APP/2026-27/1</t>
+          <t>8516/1203/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/34350/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/34233/1/</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>34350</v>
+        <v>34233</v>
       </c>
     </row>
     <row r="67">
@@ -31515,21 +31603,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RUIRU-JUJA WATER &amp; SEWERAGE COMPANY LTD</t>
+          <t>STATE DEPARTMENT FOR PARLIAMENTARY AFFAIRS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RUJWASCO/1874/APP/2026-27/2</t>
+          <t>SDPA/747/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/34426/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/34307/1/</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>34426</v>
+        <v>34307</v>
       </c>
     </row>
     <row r="68">
@@ -31543,21 +31631,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KENYA CIVIL AVIATION AUTHORITY</t>
+          <t>STATE DEPARTMENT FOR MINING</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>KCAA/919/APP/2026-27/1</t>
+          <t>SDM/794/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/34916/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/34350/1/</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>34916</v>
+        <v>34350</v>
       </c>
     </row>
     <row r="69">
@@ -31571,21 +31659,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NATIONAL INDUSTRIAL TRAINING AUTHORITY</t>
+          <t>RUIRU-JUJA WATER &amp; SEWERAGE COMPANY LTD</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NITA/1049/APP/2026-27/1</t>
+          <t>RUJWASCO/1874/APP/2026-27/2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/34987/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/34426/1/</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>34987</v>
+        <v>34426</v>
       </c>
     </row>
     <row r="70">
@@ -31599,21 +31687,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR AVIATION AND AEROSPACE DEVELOPMENT</t>
+          <t>KENYA CIVIL AVIATION AUTHORITY</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SDAAD/1000/APP/2026-27/1</t>
+          <t>KCAA/919/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/35049/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/34916/1/</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>35049</v>
+        <v>34916</v>
       </c>
     </row>
     <row r="71">
@@ -31627,21 +31715,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NATIONAL POLICE SERVICE COMMISSION</t>
+          <t>NATIONAL INDUSTRIAL TRAINING AUTHORITY</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NPSC/724/APP/2026-27/1</t>
+          <t>NITA/1049/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/35255/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/34987/1/</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>35255</v>
+        <v>34987</v>
       </c>
     </row>
     <row r="72">
@@ -31655,21 +31743,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NATIONAL SYNDEMIC DISEASES CONTROL COUNCIL</t>
+          <t>STATE DEPARTMENT FOR AVIATION AND AEROSPACE DEVELOPMENT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NSDCC/900/APP/2026-27/1</t>
+          <t>SDAAD/1000/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/35617/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/35049/1/</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>35617</v>
+        <v>35049</v>
       </c>
     </row>
     <row r="73">
@@ -31683,21 +31771,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KONZA TECHNOPOLIES DEVELOPMENT AUTHORITY</t>
+          <t>NATIONAL POLICE SERVICE COMMISSION</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KOTDA/907/APP/2026-27/1</t>
+          <t>NPSC/724/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/35691/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/35255/1/</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>35691</v>
+        <v>35255</v>
       </c>
     </row>
     <row r="74">
@@ -31711,21 +31799,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KENYA INSTITUTE OF SUPPLIES EXAMINATION BOARD</t>
+          <t>NATIONAL QUALITY CONTROL LABORATORY</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KISEB/950/APP/2026-27/1</t>
+          <t>NCQL/962/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/35738/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/35287/1/</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>35738</v>
+        <v>35287</v>
       </c>
     </row>
     <row r="75">
@@ -31739,21 +31827,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR CABINET AFFAIRS</t>
+          <t>NATIONAL SYNDEMIC DISEASES CONTROL COUNCIL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SDCA/1163/APP/2026-27/1</t>
+          <t>NSDCC/900/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/35740/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/35617/1/</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>35740</v>
+        <v>35617</v>
       </c>
     </row>
     <row r="76">
@@ -31767,21 +31855,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TEA BOARD OF KENYA</t>
+          <t>KONZA TECHNOPOLIES DEVELOPMENT AUTHORITY</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TBK/764/APP/2026-27/1</t>
+          <t>KOTDA/907/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/35847/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/35691/1/</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>35847</v>
+        <v>35691</v>
       </c>
     </row>
     <row r="77">
@@ -31795,21 +31883,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KENYA ACCREDITATION SERVICE</t>
+          <t>KENYA INSTITUTE OF SUPPLIES EXAMINATION BOARD</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KENAS/1022/APP/2026-27/1</t>
+          <t>KISEB/950/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36050/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/35738/1/</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>36050</v>
+        <v>35738</v>
       </c>
     </row>
     <row r="78">
@@ -31823,21 +31911,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TVET CURRICULUM DEVELOPMENT, ASSESSMENT AND CERTIFICATION COUNCIL</t>
+          <t>STATE DEPARTMENT FOR CABINET AFFAIRS</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>TVETCDACC/862/APP/2026-27/7</t>
+          <t>SDCA/1163/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36174/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/35740/1/</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>36174</v>
+        <v>35740</v>
       </c>
     </row>
     <row r="79">
@@ -31851,21 +31939,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>COMMISSION ON REVENUE ALLOCATION</t>
+          <t>TEA BOARD OF KENYA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CRA/725/APP/2026-27/1</t>
+          <t>TBK/764/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36250/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/35847/1/</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>36250</v>
+        <v>35847</v>
       </c>
     </row>
     <row r="80">
@@ -31879,21 +31967,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NATIONAL TRANSPORT AND SAFETY AUTHORITY</t>
+          <t>KENYA ACCREDITATION SERVICE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NTSA/922/APP/2026-27/1</t>
+          <t>KENAS/1022/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36340/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36050/1/</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>36340</v>
+        <v>36050</v>
       </c>
     </row>
     <row r="81">
@@ -31907,21 +31995,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>COMMISSION ON ADMINISTRATIVE JUSTICE</t>
+          <t>TVET CURRICULUM DEVELOPMENT, ASSESSMENT AND CERTIFICATION COUNCIL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CAJ/726/APP/2026-27/2</t>
+          <t>TVETCDACC/862/APP/2026-27/7</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36359/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36174/1/</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>36359</v>
+        <v>36174</v>
       </c>
     </row>
     <row r="82">
@@ -31935,21 +32023,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NEW KENYA PLANTERS CO-OPERATIVE UNION</t>
+          <t>NATIONAL TRANSPORT AND SAFETY AUTHORITY</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NKPCU/775/APP/2026-27/1</t>
+          <t>NTSA/922/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36376/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36340/1/</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>36376</v>
+        <v>36340</v>
       </c>
     </row>
     <row r="83">
@@ -31963,21 +32051,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>STATE DEPARTMMENT FOR SOCIAL PROTECTION AND SENIOR CITIZEN AFFAIRS</t>
+          <t>COMMISSION ON ADMINISTRATIVE JUSTICE</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SDSPSCA/981/APP/2026-27/1</t>
+          <t>CAJ/726/APP/2026-27/2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36388/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36359/1/</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>36388</v>
+        <v>36359</v>
       </c>
     </row>
     <row r="84">
@@ -31991,21 +32079,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KENYA SUGAR BOARD</t>
+          <t>NEW KENYA PLANTERS CO-OPERATIVE UNION</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KSB/765/APP/2026-27/2</t>
+          <t>NKPCU/775/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36429/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36376/1/</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>36429</v>
+        <v>36376</v>
       </c>
     </row>
     <row r="85">
@@ -32019,21 +32107,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TANA WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>STATE DEPARTMMENT FOR SOCIAL PROTECTION AND SENIOR CITIZEN AFFAIRS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>TWWDA/47943/APP/2026-27/1</t>
+          <t>SDSPSCA/981/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36451/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36388/1/</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>36451</v>
+        <v>36388</v>
       </c>
     </row>
     <row r="86">
@@ -32047,21 +32135,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR THE BLUE ECONOMY AND FISHERIES</t>
+          <t>KENYA SUGAR BOARD</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SDBEF/795/APP/2026-27/1</t>
+          <t>KSB/765/APP/2026-27/2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36485/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36429/1/</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>36485</v>
+        <v>36429</v>
       </c>
     </row>
     <row r="87">
@@ -32075,21 +32163,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NATIONAL RESEARCH FUND</t>
+          <t>ANTI-DOPING AGENCY OF KENYA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NRF/840/APP/2026-27/1</t>
+          <t>ADAK/1025/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36702/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36436/1/</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>36702</v>
+        <v>36436</v>
       </c>
     </row>
     <row r="88">
@@ -32103,21 +32191,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NAIROBI CENTRE FOR INTERNATIONAL ARBITRATION</t>
+          <t>STATE DEPARTMENT FOR THE BLUE ECONOMY AND FISHERIES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NCIA/804/APP/2026-27/1</t>
+          <t>SDBEF/795/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36885/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36485/1/</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>36885</v>
+        <v>36485</v>
       </c>
     </row>
     <row r="89">
@@ -32131,21 +32219,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HYDROLOGISTS REGISTRATION BOARD</t>
+          <t>STATE DEPARTMENT FOR INVESTMENTS PROMOTION</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>HRB/791/APP/2026-27/1</t>
+          <t>SDIP/1005/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36951/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36647/1/</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>36951</v>
+        <v>36647</v>
       </c>
     </row>
     <row r="90">
@@ -32159,21 +32247,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>KENYA COPYRIGHTS BOARD</t>
+          <t>NATIONAL RESEARCH FUND</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KECOBO/990/APP/2026-27/2</t>
+          <t>NRF/840/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36957/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36702/1/</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>36957</v>
+        <v>36702</v>
       </c>
     </row>
     <row r="91">
@@ -32187,21 +32275,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NATIONAL DEFENCE UNIVERSITY-KENYA</t>
+          <t>NAIROBI CENTRE FOR INTERNATIONAL ARBITRATION</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NDUK/1015/APP/2026-27/2</t>
+          <t>NCIA/804/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/36985/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36885/1/</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>36985</v>
+        <v>36885</v>
       </c>
     </row>
     <row r="92">
@@ -32215,21 +32303,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>KENYA NATIONAL QUALIFICATIONS AUTHORITY</t>
+          <t>STATE DEPARTMENT FOR DIASPORA AFFAIRS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>KNQA/863/APP/2026-27/1</t>
+          <t>SDDA/746/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37086/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36891/1/</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>37086</v>
+        <v>36891</v>
       </c>
     </row>
     <row r="93">
@@ -32243,21 +32331,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NATIONAL COUNCIL FOR LAW REPORTING</t>
+          <t>HYDROLOGISTS REGISTRATION BOARD</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NCLR/802/APP/2026-27/1</t>
+          <t>HRB/791/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37129/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36951/1/</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>37129</v>
+        <v>36951</v>
       </c>
     </row>
     <row r="94">
@@ -32271,21 +32359,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JOMO KENYATTA FOUNDATION</t>
+          <t>KENYA COPYRIGHTS BOARD</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>JKFDN/1167/APP/2026-27/9</t>
+          <t>KECOBO/990/APP/2026-27/2</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37212/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36957/1/</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>37212</v>
+        <v>36957</v>
       </c>
     </row>
     <row r="95">
@@ -32299,21 +32387,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NUCLEAR POWER AND ENERGY AGENCY</t>
+          <t>NATIONAL DEFENCE UNIVERSITY-KENYA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NUPEA/895/APP/2026-27/3</t>
+          <t>NDUK/1015/APP/2026-27/2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37283/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/36985/1/</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>37283</v>
+        <v>36985</v>
       </c>
     </row>
     <row r="96">
@@ -32327,21 +32415,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>UGUNJA TECHNICAL AND VOCATIONAL COLLEGE</t>
+          <t>KENYA NATIONAL QUALIFICATIONS AUTHORITY</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>8950/2058/APP/2026-27/1</t>
+          <t>KNQA/863/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37297/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/37086/1/</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>37297</v>
+        <v>37086</v>
       </c>
     </row>
     <row r="97">
@@ -32355,21 +32443,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>KENYA ACADEMY OF SPORTS</t>
+          <t>NATIONAL COUNCIL FOR LAW REPORTING</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>KAS/1026/APP/2026-27/2</t>
+          <t>NCLR/802/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37325/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/37129/1/</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>37325</v>
+        <v>37129</v>
       </c>
     </row>
     <row r="98">
@@ -32383,21 +32471,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>COMMUNICATIONS AUTHORITY OF KENYA</t>
+          <t>JOMO KENYATTA FOUNDATION</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>COMMA/1039/APP/2026-27/3</t>
+          <t>JKFDN/1167/APP/2026-27/9</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37374/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/37212/1/</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>37374</v>
+        <v>37212</v>
       </c>
     </row>
     <row r="99">
@@ -32411,21 +32499,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MEDIA COUNCIL OF KENYA</t>
+          <t>NUCLEAR POWER AND ENERGY AGENCY</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>MCK/1057/APP/2026-27/2</t>
+          <t>NUPEA/895/APP/2026-27/3</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37455/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/37283/1/</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>37455</v>
+        <v>37283</v>
       </c>
     </row>
     <row r="100">
@@ -32439,21 +32527,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR CHILDREN SERVICES</t>
+          <t>UGUNJA TECHNICAL AND VOCATIONAL COLLEGE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>STDCS/25138/APP/2026-27/1</t>
+          <t>8950/2058/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37468/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/37297/1/</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>37468</v>
+        <v>37297</v>
       </c>
     </row>
     <row r="101">
@@ -32467,21 +32555,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NATIONAL CANCER INSTITUTE OF KENYA</t>
+          <t>STATE DEPARTMENT FOR BASIC EDUCATION</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NCI/902/APP/2026-27/2</t>
+          <t>SDBE/810/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37668/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/37304/1/</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>37668</v>
+        <v>37304</v>
       </c>
     </row>
     <row r="102">
@@ -32495,21 +32583,21 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LAKE VICTORIA NORTH WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>KENYA ACADEMY OF SPORTS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LVNWWDA/709/APP/2026-27/1</t>
+          <t>KAS/1026/APP/2026-27/2</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37736/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/37325/1/</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>37736</v>
+        <v>37325</v>
       </c>
     </row>
     <row r="103">
@@ -32523,21 +32611,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KENYA CULTURAL CENTRE</t>
+          <t>WILDLIFE CLUBS OF KENYA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>KCC/991/APP/2026-27/2</t>
+          <t>WCK/49563/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37763/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/37362/1/</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>37763</v>
+        <v>37362</v>
       </c>
     </row>
     <row r="104">
@@ -32551,21 +32639,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NORTHERN WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>COMMUNICATIONS AUTHORITY OF KENYA</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NWWDA/711/APP/2026-27/1</t>
+          <t>COMMA/1039/APP/2026-27/3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37777/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/37374/1/</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>37777</v>
+        <v>37374</v>
       </c>
     </row>
     <row r="105">
@@ -32579,21 +32667,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>UNIVERSITIES FUND</t>
+          <t>STATE DEPARTMENT FOR CHILDREN SERVICES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>UFB/848/APP/2026-27/2</t>
+          <t>STDCS/25138/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37827/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/37468/1/</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>37827</v>
+        <v>37468</v>
       </c>
     </row>
     <row r="106">
@@ -32607,21 +32695,21 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>UNCLAIMED FINANCIAL ASSETS AUTHORITY</t>
+          <t>NATIONAL CANCER INSTITUTE OF KENYA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>UFFA/938/APP/2026-27/2</t>
+          <t>NCI/902/APP/2026-27/2</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/37881/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/37668/1/</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>37881</v>
+        <v>37668</v>
       </c>
     </row>
     <row r="107">
@@ -32635,21 +32723,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TOM MBOYA UNIVERSITY</t>
+          <t>STATE DEPARTMENT FOR SPORTS</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>TMU/849/APP/2026-27/3</t>
+          <t>SDS/1010/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/38007/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/37700/1/</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>38007</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="108">
@@ -32663,21 +32751,21 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>KENYA DAIRY BOARD</t>
+          <t>LAKE VICTORIA NORTH WATER WORKS DEVELOPMENT AGENCY</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>KDB/739/APP/2026-27/7</t>
+          <t>LVNWWDA/709/APP/2026-27/1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://egpkenya.go.ke/public-view-app/38157/1/</t>
+          <t>https://egpkenya.go.ke/public-view-app/37736/1/</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>38157</v>
+        <v>37736</v>
       </c>
     </row>
     <row r="109">
@@ -32691,21 +32779,413 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
+          <t>KENYA CULTURAL CENTRE</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>KCC/991/APP/2026-27/2</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/37763/1/</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>37763</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>NORTHERN WATER WORKS DEVELOPMENT AGENCY</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NWWDA/711/APP/2026-27/1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/37777/1/</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>37777</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>UNIVERSITIES FUND</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>UFB/848/APP/2026-27/2</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/37827/1/</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>37827</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TANA AND ATHI RIVERS DEVELOPMENT AUTHORITY</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>TARDA/1081/APP/2026-27/1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/37875/1/</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>37875</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>TOM MBOYA UNIVERSITY</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>TMU/849/APP/2026-27/3</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/38007/1/</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>38007</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CHUKA UNIVERSITY</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CHUKA/814/APP/2026-27/1</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/38079/1/</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>38079</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>KENYA DAIRY BOARD</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>KDB/739/APP/2026-27/7</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/38157/1/</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>38157</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>STATE DEPARTMENT FOR SCIENCE, RESEARCH AND INNOVATION</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SDSRI/1023/APP/2026-27/1</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/38287/1/</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>38287</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>TANA WATER WORKS DEVELOPMENT AGENCY</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>TWWDA/47943/APP/2026-27/2</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/38314/1/</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>38314</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>NAIROBI METROPOLITAN AREA TRANSPORT AUTHORITY</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>NAMATA/926/APP/2026-27/3</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>https://egpkenya.go.ke/public-view-app/38400/1/</t>
         </is>
       </c>
-      <c r="F109" t="n">
+      <c r="F118" t="n">
         <v>38400</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>UNCLAIMED FINANCIAL ASSETS AUTHORITY</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>UFFA/938/APP/2026-27/3</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/38446/1/</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>38446</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>COUNCIL FOR LEGAL EDUCATION</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CLE/799/APP/2026-27/3</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/38472/1/</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>38472</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>COMMISSION ON REVENUE ALLOCATION</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>CRA/725/APP/2026-27/2</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/38804/1/</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>38804</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>KENYA SCHOOL OF LAW</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>KSL/801/APP/2026-27/1</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/38820/1/</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>38820</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>MEDIA COUNCIL OF KENYA</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>MCK/1057/APP/2026-27/4</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://egpkenya.go.ke/public-view-app/39446/1/</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>39446</v>
       </c>
     </row>
   </sheetData>
@@ -32719,7 +33199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32820,7 +33300,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COUNCIL FOR LEGAL EDUCATION</t>
+          <t>NATIONAL DROUGHT MANAGEMENT AUTHORITY</t>
         </is>
       </c>
     </row>
@@ -32830,7 +33310,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NATIONAL DROUGHT MANAGEMENT AUTHORITY</t>
+          <t>PARLIAMENTARY SERVICE COMMISSION</t>
         </is>
       </c>
     </row>
@@ -32840,7 +33320,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PARLIAMENTARY SERVICE COMMISSION</t>
+          <t>KENYA WATER INSTITUTE</t>
         </is>
       </c>
     </row>
@@ -32850,7 +33330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KENYA WATER INSTITUTE</t>
+          <t>ATHI WATER WORKS DEVELOPMENT AGENCY</t>
         </is>
       </c>
     </row>
@@ -32860,7 +33340,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATHI WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>SPORTS KENYA</t>
         </is>
       </c>
     </row>
@@ -32870,7 +33350,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SPORTS KENYA</t>
+          <t>INTERGOVERNMENTAL RELATIONS TECHNICAL COMMITTEE</t>
         </is>
       </c>
     </row>
@@ -32880,7 +33360,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INTERGOVERNMENTAL RELATIONS TECHNICAL COMMITTEE</t>
+          <t>SALARIES AND REMUNERATION COMMISSION</t>
         </is>
       </c>
     </row>
@@ -32890,7 +33370,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SALARIES AND REMUNERATION COMMISSION</t>
+          <t>OFFICE OF THE DATA PROTECTION COMMISSIONER</t>
         </is>
       </c>
     </row>
@@ -32900,7 +33380,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OFFICE OF THE DATA PROTECTION COMMISSIONER</t>
+          <t>OFFICE OF THE REGISTRAR OF POLITICAL PARTIES</t>
         </is>
       </c>
     </row>
@@ -32910,7 +33390,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OFFICE OF THE REGISTRAR OF POLITICAL PARTIES</t>
+          <t>TEACHERS SERVICE COMMISSION</t>
         </is>
       </c>
     </row>
@@ -32920,7 +33400,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TEACHERS SERVICE COMMISSION</t>
+          <t>VETERINARY MEDICINES DIRECTORATE COUNCIL</t>
         </is>
       </c>
     </row>
@@ -32930,7 +33410,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VETERINARY MEDICINES DIRECTORATE COUNCIL</t>
+          <t>KERIO VALLEY DEVELOPMENT AUTHORITY</t>
         </is>
       </c>
     </row>
@@ -32940,7 +33420,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KERIO VALLEY DEVELOPMENT AUTHORITY</t>
+          <t>NATIONAL COUNCIL FOR PERSONS WITH DISABILITIES</t>
         </is>
       </c>
     </row>
@@ -32950,7 +33430,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NATIONAL COUNCIL FOR PERSONS WITH DISABILITIES</t>
+          <t>Public Benefit Organizations Regulatory Authority</t>
         </is>
       </c>
     </row>
@@ -32960,7 +33440,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Public Benefit Organizations Regulatory Authority</t>
+          <t>THE SENATE</t>
         </is>
       </c>
     </row>
@@ -32970,7 +33450,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>THE SENATE</t>
+          <t>STATE DEPARTMENT FOR HIGHER EDUCATION</t>
         </is>
       </c>
     </row>
@@ -33090,7 +33570,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KENYA NATIONAL HUMAN RIGHTS AND EQUALITY COMMISSION</t>
+          <t>STATE DEPARTMENT FOR TRADE</t>
         </is>
       </c>
     </row>
@@ -33100,7 +33580,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RETIREMENT BENEFITS AUTHORITY</t>
+          <t>KENYA NATIONAL HUMAN RIGHTS AND EQUALITY COMMISSION</t>
         </is>
       </c>
     </row>
@@ -33110,7 +33590,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KITALE NATIONAL POLYTECHNIC</t>
+          <t>RETIREMENT BENEFITS AUTHORITY</t>
         </is>
       </c>
     </row>
@@ -33120,7 +33600,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KENYA FILM COMMISSION</t>
+          <t>KITALE NATIONAL POLYTECHNIC</t>
         </is>
       </c>
     </row>
@@ -33130,7 +33610,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KENYA ROADS BOARD</t>
+          <t>NATIONAL GENDER AND EQUALITY COMMISSION</t>
         </is>
       </c>
     </row>
@@ -33140,7 +33620,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR GENDER AFFAIRS &amp; AFFIRMATIVE ACTION</t>
+          <t>KENYA FILM COMMISSION</t>
         </is>
       </c>
     </row>
@@ -33150,7 +33630,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PUBLIC SERVICE COMMISSION</t>
+          <t>KENYA ROADS BOARD</t>
         </is>
       </c>
     </row>
@@ -33160,7 +33640,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OFFICE OF THE AUDITOR-GENERAL</t>
+          <t>STATE DEPARTMENT FOR GENDER AFFAIRS &amp; AFFIRMATIVE ACTION</t>
         </is>
       </c>
     </row>
@@ -33170,7 +33650,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ETHICS AND ANTI-CORRUPTION COMMISSION</t>
+          <t>PUBLIC SERVICE COMMISSION</t>
         </is>
       </c>
     </row>
@@ -33180,7 +33660,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KENYA PLANT HEALTH INSPECTORATE SERVICES</t>
+          <t>OFFICE OF THE AUDITOR-GENERAL</t>
         </is>
       </c>
     </row>
@@ -33190,7 +33670,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NATIONAL BIO-SAFETY AUTHORITY</t>
+          <t>ETHICS AND ANTI-CORRUPTION COMMISSION</t>
         </is>
       </c>
     </row>
@@ -33200,7 +33680,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EXECUTIVE OFFICE OF THE PRESIDENT</t>
+          <t>KENYA PLANT HEALTH INSPECTORATE SERVICES</t>
         </is>
       </c>
     </row>
@@ -33210,7 +33690,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PEST CONTROL PRODUCTS BOARD</t>
+          <t>NATIONAL BIO-SAFETY AUTHORITY</t>
         </is>
       </c>
     </row>
@@ -33220,7 +33700,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MOI TEACHING AND REFERRAL HOSPITAL</t>
+          <t>EXECUTIVE OFFICE OF THE PRESIDENT</t>
         </is>
       </c>
     </row>
@@ -33230,7 +33710,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR PUBLIC SERVICE AND HUMAN CAPITAL DEVELOPMENT</t>
+          <t>PEST CONTROL PRODUCTS BOARD</t>
         </is>
       </c>
     </row>
@@ -33240,7 +33720,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KENYA NATIONAL TRADING CORPORATION</t>
+          <t>MOI TEACHING AND REFERRAL HOSPITAL</t>
         </is>
       </c>
     </row>
@@ -33250,7 +33730,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR INTERNAL SECURITY AND NATIONAL ADMINISTRATION</t>
+          <t>STATE DEPARTMENT FOR PUBLIC SERVICE AND HUMAN CAPITAL DEVELOPMENT</t>
         </is>
       </c>
     </row>
@@ -33260,7 +33740,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NUMERICAL MACHINING COMPLEX</t>
+          <t>KENYA NATIONAL TRADING CORPORATION</t>
         </is>
       </c>
     </row>
@@ -33270,7 +33750,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>THE NATIONAL TREASURY</t>
+          <t>STATE DEPARTMENT FOR INTERNAL SECURITY AND NATIONAL ADMINISTRATION</t>
         </is>
       </c>
     </row>
@@ -33280,7 +33760,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RIFT VALLEY TECHNICAL TRAINING INSTITUTE</t>
+          <t>NUMERICAL MACHINING COMPLEX</t>
         </is>
       </c>
     </row>
@@ -33290,7 +33770,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR PUBLIC INVESTMENT &amp; ASSET MANAGEMENT</t>
+          <t>THE NATIONAL TREASURY</t>
         </is>
       </c>
     </row>
@@ -33300,7 +33780,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>POLICY HOLDERS COMPENSATION FUND</t>
+          <t>RIFT VALLEY TECHNICAL TRAINING INSTITUTE</t>
         </is>
       </c>
     </row>
@@ -33310,7 +33790,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KENYA SPACE AGENCY</t>
+          <t>STATE DEPARTMENT FOR PUBLIC INVESTMENT &amp; ASSET MANAGEMENT</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33800,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FINANCIAL INCLUSION FUND</t>
+          <t>POLICY HOLDERS COMPENSATION FUND</t>
         </is>
       </c>
     </row>
@@ -33330,7 +33810,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OFFICE OF THE PRIME CABINET SECRETARY</t>
+          <t>KENYA SPACE AGENCY</t>
         </is>
       </c>
     </row>
@@ -33340,7 +33820,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KENYA INVESTMENT AUTHORITY</t>
+          <t>FINANCIAL INCLUSION FUND</t>
         </is>
       </c>
     </row>
@@ -33350,7 +33830,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>INDEPENDENT POLICING OVERSIGHT AUTHORITY</t>
+          <t>OFFICE OF THE PRIME CABINET SECRETARY</t>
         </is>
       </c>
     </row>
@@ -33360,7 +33840,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>THE NATIONAL HEROES COUNCIL</t>
+          <t>KENYA INVESTMENT AUTHORITY</t>
         </is>
       </c>
     </row>
@@ -33370,7 +33850,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR PARLIAMENTARY AFFAIRS</t>
+          <t>INDEPENDENT POLICING OVERSIGHT AUTHORITY</t>
         </is>
       </c>
     </row>
@@ -33380,7 +33860,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR MINING</t>
+          <t>THE NATIONAL HEROES COUNCIL</t>
         </is>
       </c>
     </row>
@@ -33390,7 +33870,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RUIRU-JUJA WATER &amp; SEWERAGE COMPANY LTD</t>
+          <t>STATE DEPARTMENT FOR PARLIAMENTARY AFFAIRS</t>
         </is>
       </c>
     </row>
@@ -33400,7 +33880,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KENYA CIVIL AVIATION AUTHORITY</t>
+          <t>STATE DEPARTMENT FOR MINING</t>
         </is>
       </c>
     </row>
@@ -33410,7 +33890,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NATIONAL INDUSTRIAL TRAINING AUTHORITY</t>
+          <t>RUIRU-JUJA WATER &amp; SEWERAGE COMPANY LTD</t>
         </is>
       </c>
     </row>
@@ -33420,7 +33900,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR AVIATION AND AEROSPACE DEVELOPMENT</t>
+          <t>KENYA CIVIL AVIATION AUTHORITY</t>
         </is>
       </c>
     </row>
@@ -33430,7 +33910,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NATIONAL POLICE SERVICE COMMISSION</t>
+          <t>NATIONAL INDUSTRIAL TRAINING AUTHORITY</t>
         </is>
       </c>
     </row>
@@ -33440,7 +33920,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NATIONAL SYNDEMIC DISEASES CONTROL COUNCIL</t>
+          <t>STATE DEPARTMENT FOR AVIATION AND AEROSPACE DEVELOPMENT</t>
         </is>
       </c>
     </row>
@@ -33450,7 +33930,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>KONZA TECHNOPOLIES DEVELOPMENT AUTHORITY</t>
+          <t>NATIONAL POLICE SERVICE COMMISSION</t>
         </is>
       </c>
     </row>
@@ -33460,7 +33940,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>KENYA INSTITUTE OF SUPPLIES EXAMINATION BOARD</t>
+          <t>NATIONAL QUALITY CONTROL LABORATORY</t>
         </is>
       </c>
     </row>
@@ -33470,7 +33950,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR CABINET AFFAIRS</t>
+          <t>NATIONAL SYNDEMIC DISEASES CONTROL COUNCIL</t>
         </is>
       </c>
     </row>
@@ -33480,7 +33960,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TEA BOARD OF KENYA</t>
+          <t>KONZA TECHNOPOLIES DEVELOPMENT AUTHORITY</t>
         </is>
       </c>
     </row>
@@ -33490,7 +33970,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KENYA ACCREDITATION SERVICE</t>
+          <t>KENYA INSTITUTE OF SUPPLIES EXAMINATION BOARD</t>
         </is>
       </c>
     </row>
@@ -33500,7 +33980,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TVET CURRICULUM DEVELOPMENT, ASSESSMENT AND CERTIFICATION COUNCIL</t>
+          <t>STATE DEPARTMENT FOR CABINET AFFAIRS</t>
         </is>
       </c>
     </row>
@@ -33510,7 +33990,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>COMMISSION ON REVENUE ALLOCATION</t>
+          <t>TEA BOARD OF KENYA</t>
         </is>
       </c>
     </row>
@@ -33520,7 +34000,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NATIONAL TRANSPORT AND SAFETY AUTHORITY</t>
+          <t>KENYA ACCREDITATION SERVICE</t>
         </is>
       </c>
     </row>
@@ -33530,7 +34010,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>COMMISSION ON ADMINISTRATIVE JUSTICE</t>
+          <t>TVET CURRICULUM DEVELOPMENT, ASSESSMENT AND CERTIFICATION COUNCIL</t>
         </is>
       </c>
     </row>
@@ -33540,7 +34020,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NEW KENYA PLANTERS CO-OPERATIVE UNION</t>
+          <t>NATIONAL TRANSPORT AND SAFETY AUTHORITY</t>
         </is>
       </c>
     </row>
@@ -33550,7 +34030,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>STATE DEPARTMMENT FOR SOCIAL PROTECTION AND SENIOR CITIZEN AFFAIRS</t>
+          <t>COMMISSION ON ADMINISTRATIVE JUSTICE</t>
         </is>
       </c>
     </row>
@@ -33560,7 +34040,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KENYA SUGAR BOARD</t>
+          <t>NEW KENYA PLANTERS CO-OPERATIVE UNION</t>
         </is>
       </c>
     </row>
@@ -33570,7 +34050,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TANA WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>STATE DEPARTMMENT FOR SOCIAL PROTECTION AND SENIOR CITIZEN AFFAIRS</t>
         </is>
       </c>
     </row>
@@ -33580,7 +34060,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR THE BLUE ECONOMY AND FISHERIES</t>
+          <t>KENYA SUGAR BOARD</t>
         </is>
       </c>
     </row>
@@ -33590,7 +34070,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NATIONAL RESEARCH FUND</t>
+          <t>ANTI-DOPING AGENCY OF KENYA</t>
         </is>
       </c>
     </row>
@@ -33600,7 +34080,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NAIROBI CENTRE FOR INTERNATIONAL ARBITRATION</t>
+          <t>STATE DEPARTMENT FOR THE BLUE ECONOMY AND FISHERIES</t>
         </is>
       </c>
     </row>
@@ -33610,7 +34090,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HYDROLOGISTS REGISTRATION BOARD</t>
+          <t>STATE DEPARTMENT FOR INVESTMENTS PROMOTION</t>
         </is>
       </c>
     </row>
@@ -33620,7 +34100,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KENYA COPYRIGHTS BOARD</t>
+          <t>NATIONAL RESEARCH FUND</t>
         </is>
       </c>
     </row>
@@ -33630,7 +34110,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NATIONAL DEFENCE UNIVERSITY-KENYA</t>
+          <t>NAIROBI CENTRE FOR INTERNATIONAL ARBITRATION</t>
         </is>
       </c>
     </row>
@@ -33640,7 +34120,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KENYA NATIONAL QUALIFICATIONS AUTHORITY</t>
+          <t>STATE DEPARTMENT FOR DIASPORA AFFAIRS</t>
         </is>
       </c>
     </row>
@@ -33650,7 +34130,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NATIONAL COUNCIL FOR LAW REPORTING</t>
+          <t>HYDROLOGISTS REGISTRATION BOARD</t>
         </is>
       </c>
     </row>
@@ -33660,7 +34140,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JOMO KENYATTA FOUNDATION</t>
+          <t>KENYA COPYRIGHTS BOARD</t>
         </is>
       </c>
     </row>
@@ -33670,7 +34150,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NUCLEAR POWER AND ENERGY AGENCY</t>
+          <t>NATIONAL DEFENCE UNIVERSITY-KENYA</t>
         </is>
       </c>
     </row>
@@ -33680,7 +34160,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>UGUNJA TECHNICAL AND VOCATIONAL COLLEGE</t>
+          <t>KENYA NATIONAL QUALIFICATIONS AUTHORITY</t>
         </is>
       </c>
     </row>
@@ -33690,7 +34170,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KENYA ACADEMY OF SPORTS</t>
+          <t>NATIONAL COUNCIL FOR LAW REPORTING</t>
         </is>
       </c>
     </row>
@@ -33700,7 +34180,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>COMMUNICATIONS AUTHORITY OF KENYA</t>
+          <t>JOMO KENYATTA FOUNDATION</t>
         </is>
       </c>
     </row>
@@ -33710,7 +34190,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MEDIA COUNCIL OF KENYA</t>
+          <t>NUCLEAR POWER AND ENERGY AGENCY</t>
         </is>
       </c>
     </row>
@@ -33720,7 +34200,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR CHILDREN SERVICES</t>
+          <t>UGUNJA TECHNICAL AND VOCATIONAL COLLEGE</t>
         </is>
       </c>
     </row>
@@ -33730,7 +34210,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NATIONAL CANCER INSTITUTE OF KENYA</t>
+          <t>STATE DEPARTMENT FOR BASIC EDUCATION</t>
         </is>
       </c>
     </row>
@@ -33740,7 +34220,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LAKE VICTORIA NORTH WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>KENYA ACADEMY OF SPORTS</t>
         </is>
       </c>
     </row>
@@ -33750,7 +34230,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KENYA CULTURAL CENTRE</t>
+          <t>WILDLIFE CLUBS OF KENYA</t>
         </is>
       </c>
     </row>
@@ -33760,7 +34240,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NORTHERN WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>COMMUNICATIONS AUTHORITY OF KENYA</t>
         </is>
       </c>
     </row>
@@ -33770,7 +34250,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>UNIVERSITIES FUND</t>
+          <t>STATE DEPARTMENT FOR CHILDREN SERVICES</t>
         </is>
       </c>
     </row>
@@ -33780,7 +34260,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>UNCLAIMED FINANCIAL ASSETS AUTHORITY</t>
+          <t>NATIONAL CANCER INSTITUTE OF KENYA</t>
         </is>
       </c>
     </row>
@@ -33790,7 +34270,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TOM MBOYA UNIVERSITY</t>
+          <t>STATE DEPARTMENT FOR SPORTS</t>
         </is>
       </c>
     </row>
@@ -33800,7 +34280,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KENYA DAIRY BOARD</t>
+          <t>LAKE VICTORIA NORTH WATER WORKS DEVELOPMENT AGENCY</t>
         </is>
       </c>
     </row>
@@ -33810,7 +34290,147 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
+          <t>KENYA CULTURAL CENTRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NORTHERN WATER WORKS DEVELOPMENT AGENCY</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>UNIVERSITIES FUND</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TANA AND ATHI RIVERS DEVELOPMENT AUTHORITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TOM MBOYA UNIVERSITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CHUKA UNIVERSITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>KENYA DAIRY BOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>STATE DEPARTMENT FOR SCIENCE, RESEARCH AND INNOVATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TANA WATER WORKS DEVELOPMENT AGENCY</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
           <t>NAIROBI METROPOLITAN AREA TRANSPORT AUTHORITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>UNCLAIMED FINANCIAL ASSETS AUTHORITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>COUNCIL FOR LEGAL EDUCATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>COMMISSION ON REVENUE ALLOCATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>KENYA SCHOOL OF LAW</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>MEDIA COUNCIL OF KENYA</t>
         </is>
       </c>
     </row>
@@ -33825,7 +34445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34021,17 +34641,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COUNCIL FOR LEGAL EDUCATION</t>
+          <t>NATIONAL DROUGHT MANAGEMENT AUTHORITY</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>Ksh95,593,383.00</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Ksh876,464,761.00</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -34041,12 +34661,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NATIONAL DROUGHT MANAGEMENT AUTHORITY</t>
+          <t>PARLIAMENTARY SERVICE COMMISSION</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>Ksh876,464,761.00</t>
+          <t>Ksh385,017,589.00</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -34061,12 +34681,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PARLIAMENTARY SERVICE COMMISSION</t>
+          <t>KENYA WATER INSTITUTE</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>Ksh385,017,589.00</t>
+          <t>Ksh98,355,714.00</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
@@ -34081,12 +34701,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KENYA WATER INSTITUTE</t>
+          <t>ATHI WATER WORKS DEVELOPMENT AGENCY</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>Ksh98,355,714.00</t>
+          <t>Ksh691,747,930.00</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -34101,12 +34721,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATHI WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>SPORTS KENYA</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>Ksh691,747,930.00</t>
+          <t>Ksh255,559,470.00</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -34121,17 +34741,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SPORTS KENYA</t>
+          <t>INTERGOVERNMENTAL RELATIONS TECHNICAL COMMITTEE</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>Ksh255,559,470.00</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Ksh116,279,897.85</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>Doing</t>
         </is>
       </c>
     </row>
@@ -34141,17 +34761,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INTERGOVERNMENTAL RELATIONS TECHNICAL COMMITTEE</t>
+          <t>SALARIES AND REMUNERATION COMMISSION</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>Ksh116,279,897.85</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>Doing</t>
+          <t>Ksh418,344,661.36</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -34161,12 +34781,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SALARIES AND REMUNERATION COMMISSION</t>
+          <t>OFFICE OF THE DATA PROTECTION COMMISSIONER</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>Ksh418,344,661.36</t>
+          <t>Ksh142,435,207.00</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -34181,12 +34801,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OFFICE OF THE DATA PROTECTION COMMISSIONER</t>
+          <t>OFFICE OF THE REGISTRAR OF POLITICAL PARTIES</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>Ksh142,435,207.00</t>
+          <t>Ksh280,754,302.47</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -34201,12 +34821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OFFICE OF THE REGISTRAR OF POLITICAL PARTIES</t>
+          <t>TEACHERS SERVICE COMMISSION</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>Ksh280,754,302.47</t>
+          <t>Ksh778,018,315.01</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -34221,12 +34841,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TEACHERS SERVICE COMMISSION</t>
+          <t>VETERINARY MEDICINES DIRECTORATE COUNCIL</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>Ksh778,018,315.01</t>
+          <t>Ksh63,605,213.31</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
@@ -34241,12 +34861,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VETERINARY MEDICINES DIRECTORATE COUNCIL</t>
+          <t>KERIO VALLEY DEVELOPMENT AUTHORITY</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>Ksh63,605,213.31</t>
+          <t>Ksh157,141,036.00</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -34261,12 +34881,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KERIO VALLEY DEVELOPMENT AUTHORITY</t>
+          <t>NATIONAL COUNCIL FOR PERSONS WITH DISABILITIES</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>Ksh157,141,036.00</t>
+          <t>Ksh276,122,265.00</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
@@ -34281,12 +34901,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NATIONAL COUNCIL FOR PERSONS WITH DISABILITIES</t>
+          <t>Public Benefit Organizations Regulatory Authority</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>Ksh276,122,265.00</t>
+          <t>Ksh68,516,792.00</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -34301,12 +34921,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Public Benefit Organizations Regulatory Authority</t>
+          <t>THE SENATE</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>Ksh68,516,792.00</t>
+          <t>Ksh1,051,507,414.00</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
@@ -34321,17 +34941,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>THE SENATE</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>Ksh1,051,507,414.00</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>STATE DEPARTMENT FOR HIGHER EDUCATION</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>226909162.32</v>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -34561,17 +35179,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KENYA NATIONAL HUMAN RIGHTS AND EQUALITY COMMISSION</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>Ksh47,245,579.00</t>
-        </is>
-      </c>
-      <c r="D37" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>STATE DEPARTMENT FOR TRADE</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>653627215.96</v>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -34581,12 +35197,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RETIREMENT BENEFITS AUTHORITY</t>
+          <t>KENYA NATIONAL HUMAN RIGHTS AND EQUALITY COMMISSION</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Ksh218,604,665.00</t>
+          <t>Ksh47,245,579.00</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -34601,17 +35217,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KITALE NATIONAL POLYTECHNIC</t>
+          <t>RETIREMENT BENEFITS AUTHORITY</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Ksh399,307,334.00</t>
+          <t>Ksh218,604,665.00</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>Doing</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -34621,17 +35237,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KENYA FILM COMMISSION</t>
+          <t>KITALE NATIONAL POLYTECHNIC</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Ksh56,850,422.96</t>
+          <t>Ksh399,307,334.00</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Doing</t>
         </is>
       </c>
     </row>
@@ -34641,17 +35257,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KENYA ROADS BOARD</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>Ksh422,430,792.00</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>NATIONAL GENDER AND EQUALITY COMMISSION</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>22861832</v>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -34661,12 +35275,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR GENDER AFFAIRS &amp; AFFIRMATIVE ACTION</t>
+          <t>KENYA FILM COMMISSION</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Ksh203,355,904.00</t>
+          <t>Ksh56,850,422.96</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -34681,17 +35295,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PUBLIC SERVICE COMMISSION</t>
+          <t>KENYA ROADS BOARD</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>Ksh298,619,780.00</t>
-        </is>
-      </c>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Ksh422,430,792.00</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -34701,12 +35315,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OFFICE OF THE AUDITOR-GENERAL</t>
+          <t>STATE DEPARTMENT FOR GENDER AFFAIRS &amp; AFFIRMATIVE ACTION</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>Ksh681,385,658.40</t>
+          <t>Ksh203,355,904.00</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -34721,17 +35335,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ETHICS AND ANTI-CORRUPTION COMMISSION</t>
+          <t>PUBLIC SERVICE COMMISSION</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Ksh589,775,337.00</t>
-        </is>
-      </c>
-      <c r="D45" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Ksh298,619,780.00</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -34741,12 +35355,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KENYA PLANT HEALTH INSPECTORATE SERVICES</t>
+          <t>OFFICE OF THE AUDITOR-GENERAL</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>Ksh1,149,229,628.10</t>
+          <t>Ksh681,385,658.40</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -34761,12 +35375,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NATIONAL BIO-SAFETY AUTHORITY</t>
+          <t>ETHICS AND ANTI-CORRUPTION COMMISSION</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>Ksh129,286,884.00</t>
+          <t>Ksh589,775,337.00</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -34781,12 +35395,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EXECUTIVE OFFICE OF THE PRESIDENT</t>
+          <t>KENYA PLANT HEALTH INSPECTORATE SERVICES</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>Ksh1,734,620,741.00</t>
+          <t>Ksh1,149,229,628.10</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
@@ -34801,12 +35415,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PEST CONTROL PRODUCTS BOARD</t>
+          <t>NATIONAL BIO-SAFETY AUTHORITY</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>Ksh347,783,823.72</t>
+          <t>Ksh129,286,884.00</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -34821,12 +35435,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MOI TEACHING AND REFERRAL HOSPITAL</t>
+          <t>EXECUTIVE OFFICE OF THE PRESIDENT</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>Ksh2,007,418,473.13</t>
+          <t>Ksh1,734,620,741.00</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
@@ -34841,12 +35455,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR PUBLIC SERVICE AND HUMAN CAPITAL DEVELOPMENT</t>
+          <t>PEST CONTROL PRODUCTS BOARD</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>Ksh1,421,567,745.00</t>
+          <t>Ksh347,783,823.72</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -34861,12 +35475,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KENYA NATIONAL TRADING CORPORATION</t>
+          <t>MOI TEACHING AND REFERRAL HOSPITAL</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>Ksh97,322,055.00</t>
+          <t>Ksh2,007,418,473.13</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
@@ -34881,12 +35495,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR INTERNAL SECURITY AND NATIONAL ADMINISTRATION</t>
+          <t>STATE DEPARTMENT FOR PUBLIC SERVICE AND HUMAN CAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>Ksh1,346,080,393.00</t>
+          <t>Ksh1,421,567,745.00</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -34901,12 +35515,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NUMERICAL MACHINING COMPLEX</t>
+          <t>KENYA NATIONAL TRADING CORPORATION</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>Ksh601,196,306.00</t>
+          <t>Ksh97,322,055.00</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
@@ -34921,12 +35535,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>THE NATIONAL TREASURY</t>
+          <t>STATE DEPARTMENT FOR INTERNAL SECURITY AND NATIONAL ADMINISTRATION</t>
         </is>
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>Ksh799,734,940.00</t>
+          <t>Ksh1,346,080,393.00</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
@@ -34941,17 +35555,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RIFT VALLEY TECHNICAL TRAINING INSTITUTE</t>
+          <t>NUMERICAL MACHINING COMPLEX</t>
         </is>
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>Ksh395,626,130.00</t>
-        </is>
-      </c>
-      <c r="D56" s="19" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Ksh601,196,306.00</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -34961,12 +35575,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR PUBLIC INVESTMENT &amp; ASSET MANAGEMENT</t>
+          <t>THE NATIONAL TREASURY</t>
         </is>
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>Ksh543,656,528.00</t>
+          <t>Ksh799,734,940.00</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -34981,17 +35595,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>POLICY HOLDERS COMPENSATION FUND</t>
+          <t>RIFT VALLEY TECHNICAL TRAINING INSTITUTE</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>Ksh92,054,515.00</t>
-        </is>
-      </c>
-      <c r="D58" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Ksh395,626,130.00</t>
+        </is>
+      </c>
+      <c r="D58" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -35001,12 +35615,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KENYA SPACE AGENCY</t>
+          <t>STATE DEPARTMENT FOR PUBLIC INVESTMENT &amp; ASSET MANAGEMENT</t>
         </is>
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>Ksh155,298,910.00</t>
+          <t>Ksh543,656,528.00</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
@@ -35021,12 +35635,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FINANCIAL INCLUSION FUND</t>
+          <t>POLICY HOLDERS COMPENSATION FUND</t>
         </is>
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>Ksh81,796,560.00</t>
+          <t>Ksh92,054,515.00</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -35041,12 +35655,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OFFICE OF THE PRIME CABINET SECRETARY</t>
+          <t>KENYA SPACE AGENCY</t>
         </is>
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>Ksh318,784,629.79</t>
+          <t>Ksh155,298,910.00</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -35061,12 +35675,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KENYA INVESTMENT AUTHORITY</t>
+          <t>FINANCIAL INCLUSION FUND</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>Ksh23,296,200.00</t>
+          <t>Ksh81,796,560.00</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -35081,12 +35695,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>INDEPENDENT POLICING OVERSIGHT AUTHORITY</t>
+          <t>OFFICE OF THE PRIME CABINET SECRETARY</t>
         </is>
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>Ksh245,344,108.00</t>
+          <t>Ksh318,784,629.79</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -35101,12 +35715,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>THE NATIONAL HEROES COUNCIL</t>
+          <t>KENYA INVESTMENT AUTHORITY</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>Ksh68,755,367.00</t>
+          <t>Ksh23,296,200.00</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -35121,12 +35735,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR PARLIAMENTARY AFFAIRS</t>
+          <t>INDEPENDENT POLICING OVERSIGHT AUTHORITY</t>
         </is>
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>Ksh90,666,488.00</t>
+          <t>Ksh245,344,108.00</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -35141,12 +35755,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR MINING</t>
+          <t>THE NATIONAL HEROES COUNCIL</t>
         </is>
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>Ksh667,650,453.00</t>
+          <t>Ksh68,755,367.00</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -35161,12 +35775,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RUIRU-JUJA WATER &amp; SEWERAGE COMPANY LTD</t>
+          <t>STATE DEPARTMENT FOR PARLIAMENTARY AFFAIRS</t>
         </is>
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>Ksh1,107,949,283.90</t>
+          <t>Ksh90,666,488.00</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -35181,15 +35795,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KENYA CIVIL AVIATION AUTHORITY</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="n">
-        <v>1947774941.08</v>
-      </c>
-      <c r="D68" s="21" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>STATE DEPARTMENT FOR MINING</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>Ksh667,650,453.00</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -35199,12 +35815,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NATIONAL INDUSTRIAL TRAINING AUTHORITY</t>
+          <t>RUIRU-JUJA WATER &amp; SEWERAGE COMPANY LTD</t>
         </is>
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>Ksh876,223,320.00</t>
+          <t>Ksh1,107,949,283.90</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -35219,17 +35835,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR AVIATION AND AEROSPACE DEVELOPMENT</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="inlineStr">
-        <is>
-          <t>Ksh247,946,964.00</t>
-        </is>
-      </c>
-      <c r="D70" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>KENYA CIVIL AVIATION AUTHORITY</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="n">
+        <v>1947774941.08</v>
+      </c>
+      <c r="D70" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -35239,15 +35853,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NATIONAL POLICE SERVICE COMMISSION</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="n">
-        <v>345536380</v>
-      </c>
-      <c r="D71" s="21" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>NATIONAL INDUSTRIAL TRAINING AUTHORITY</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>Ksh876,223,320.00</t>
+        </is>
+      </c>
+      <c r="D71" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -35257,12 +35873,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NATIONAL SYNDEMIC DISEASES CONTROL COUNCIL</t>
+          <t>STATE DEPARTMENT FOR AVIATION AND AEROSPACE DEVELOPMENT</t>
         </is>
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>Ksh374,533,707.00</t>
+          <t>Ksh247,946,964.00</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -35277,17 +35893,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>KONZA TECHNOPOLIES DEVELOPMENT AUTHORITY</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="inlineStr">
-        <is>
-          <t>Ksh395,951,116.06</t>
-        </is>
-      </c>
-      <c r="D73" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>NATIONAL POLICE SERVICE COMMISSION</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="n">
+        <v>345536380</v>
+      </c>
+      <c r="D73" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -35297,17 +35911,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>KENYA INSTITUTE OF SUPPLIES EXAMINATION BOARD</t>
-        </is>
-      </c>
-      <c r="C74" s="18" t="inlineStr">
-        <is>
-          <t>Ksh47,463,550.00</t>
-        </is>
-      </c>
-      <c r="D74" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>NATIONAL QUALITY CONTROL LABORATORY</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="n">
+        <v>141047378</v>
+      </c>
+      <c r="D74" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -35317,12 +35929,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR CABINET AFFAIRS</t>
+          <t>NATIONAL SYNDEMIC DISEASES CONTROL COUNCIL</t>
         </is>
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>Ksh54,668,575.00</t>
+          <t>Ksh374,533,707.00</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -35337,12 +35949,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TEA BOARD OF KENYA</t>
+          <t>KONZA TECHNOPOLIES DEVELOPMENT AUTHORITY</t>
         </is>
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>Ksh179,035,750.00</t>
+          <t>Ksh395,951,116.06</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -35357,12 +35969,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KENYA ACCREDITATION SERVICE</t>
+          <t>KENYA INSTITUTE OF SUPPLIES EXAMINATION BOARD</t>
         </is>
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>Ksh62,168,833.64</t>
+          <t>Ksh47,463,550.00</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -35377,12 +35989,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TVET CURRICULUM DEVELOPMENT, ASSESSMENT AND CERTIFICATION COUNCIL</t>
+          <t>STATE DEPARTMENT FOR CABINET AFFAIRS</t>
         </is>
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>Ksh962,663,500.00</t>
+          <t>Ksh54,668,575.00</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -35397,12 +36009,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>COMMISSION ON REVENUE ALLOCATION</t>
+          <t>TEA BOARD OF KENYA</t>
         </is>
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>Ksh85,393,787.00</t>
+          <t>Ksh179,035,750.00</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -35417,22 +36029,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NATIONAL TRANSPORT AND SAFETY AUTHORITY</t>
+          <t>KENYA ACCREDITATION SERVICE</t>
         </is>
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>Ksh1,320,869,596.00</t>
+          <t>Ksh62,168,833.64</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">template </t>
         </is>
       </c>
     </row>
@@ -35442,22 +36049,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>COMMISSION ON ADMINISTRATIVE JUSTICE</t>
+          <t>TVET CURRICULUM DEVELOPMENT, ASSESSMENT AND CERTIFICATION COUNCIL</t>
         </is>
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>Ksh42,637,290.00</t>
+          <t>Ksh962,663,500.00</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">template </t>
         </is>
       </c>
     </row>
@@ -35467,22 +36069,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NEW KENYA PLANTERS CO-OPERATIVE UNION</t>
+          <t>NATIONAL TRANSPORT AND SAFETY AUTHORITY</t>
         </is>
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>Ksh1,484,081,575.00</t>
-        </is>
-      </c>
-      <c r="D82" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">template </t>
+          <t>Ksh1,320,869,596.00</t>
+        </is>
+      </c>
+      <c r="D82" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
@@ -35492,22 +36089,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>STATE DEPARTMMENT FOR SOCIAL PROTECTION AND SENIOR CITIZEN AFFAIRS</t>
+          <t>COMMISSION ON ADMINISTRATIVE JUSTICE</t>
         </is>
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>Ksh161,758,809.00</t>
-        </is>
-      </c>
-      <c r="D83" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">template </t>
+          <t>Ksh42,637,290.00</t>
+        </is>
+      </c>
+      <c r="D83" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
@@ -35517,17 +36109,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KENYA SUGAR BOARD</t>
+          <t>NEW KENYA PLANTERS CO-OPERATIVE UNION</t>
         </is>
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>Ksh1,321,817,889.00</t>
-        </is>
-      </c>
-      <c r="D84" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Ksh1,484,081,575.00</t>
+        </is>
+      </c>
+      <c r="D84" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
@@ -35537,17 +36129,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TANA WATER WORKS DEVELOPMENT AGENCY</t>
+          <t>STATE DEPARTMMENT FOR SOCIAL PROTECTION AND SENIOR CITIZEN AFFAIRS</t>
         </is>
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>Ksh540,425,718.00</t>
+          <t>Ksh161,758,809.00</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">template </t>
         </is>
       </c>
     </row>
@@ -35557,12 +36154,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR THE BLUE ECONOMY AND FISHERIES</t>
+          <t>KENYA SUGAR BOARD</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>Ksh51,408,378.00</t>
+          <t>Ksh1,321,817,889.00</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -35577,17 +36174,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NATIONAL RESEARCH FUND</t>
-        </is>
-      </c>
-      <c r="C87" s="18" t="inlineStr">
-        <is>
-          <t>Ksh33,639,363.00</t>
-        </is>
-      </c>
-      <c r="D87" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>ANTI-DOPING AGENCY OF KENYA</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="n">
+        <v>363664246.95</v>
+      </c>
+      <c r="D87" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -35597,17 +36192,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NAIROBI CENTRE FOR INTERNATIONAL ARBITRATION</t>
+          <t>STATE DEPARTMENT FOR THE BLUE ECONOMY AND FISHERIES</t>
         </is>
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>Ksh41,019,947.00</t>
+          <t>Ksh51,408,378.00</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>template</t>
         </is>
       </c>
     </row>
@@ -35617,17 +36217,15 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HYDROLOGISTS REGISTRATION BOARD</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="inlineStr">
-        <is>
-          <t>Ksh20,842,578.00</t>
-        </is>
-      </c>
-      <c r="D89" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>STATE DEPARTMENT FOR INVESTMENTS PROMOTION</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n">
+        <v>66055267</v>
+      </c>
+      <c r="D89" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -35637,17 +36235,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KENYA COPYRIGHTS BOARD</t>
+          <t>NATIONAL RESEARCH FUND</t>
         </is>
       </c>
       <c r="C90" s="18" t="inlineStr">
         <is>
-          <t>Ksh20,551,040.00</t>
+          <t>Ksh33,639,363.00</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>template</t>
         </is>
       </c>
     </row>
@@ -35657,17 +36260,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NATIONAL DEFENCE UNIVERSITY-KENYA</t>
+          <t>NAIROBI CENTRE FOR INTERNATIONAL ARBITRATION</t>
         </is>
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>Ksh160,696,531.60</t>
+          <t>Ksh41,019,947.00</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>template</t>
         </is>
       </c>
     </row>
@@ -35677,17 +36285,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KENYA NATIONAL QUALIFICATIONS AUTHORITY</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="inlineStr">
-        <is>
-          <t>Ksh24,786,944.00</t>
-        </is>
-      </c>
-      <c r="D92" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>STATE DEPARTMENT FOR DIASPORA AFFAIRS</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="n">
+        <v>197493600</v>
+      </c>
+      <c r="D92" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -35697,17 +36303,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NATIONAL COUNCIL FOR LAW REPORTING</t>
+          <t>HYDROLOGISTS REGISTRATION BOARD</t>
         </is>
       </c>
       <c r="C93" s="18" t="inlineStr">
         <is>
-          <t>Ksh127,635,300.00</t>
+          <t>Ksh20,842,578.00</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>template</t>
         </is>
       </c>
     </row>
@@ -35717,17 +36328,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JOMO KENYATTA FOUNDATION</t>
+          <t>KENYA COPYRIGHTS BOARD</t>
         </is>
       </c>
       <c r="C94" s="18" t="inlineStr">
         <is>
-          <t>Ksh1,533,997,510.00</t>
-        </is>
-      </c>
-      <c r="D94" s="19" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Ksh20,551,040.00</t>
+        </is>
+      </c>
+      <c r="D94" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>template</t>
         </is>
       </c>
     </row>
@@ -35737,17 +36353,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NUCLEAR POWER AND ENERGY AGENCY</t>
+          <t>NATIONAL DEFENCE UNIVERSITY-KENYA</t>
         </is>
       </c>
       <c r="C95" s="18" t="inlineStr">
         <is>
-          <t>Ksh265,915,508.00</t>
+          <t>Ksh160,696,531.60</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>template</t>
         </is>
       </c>
     </row>
@@ -35757,17 +36378,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>UGUNJA TECHNICAL AND VOCATIONAL COLLEGE</t>
+          <t>KENYA NATIONAL QUALIFICATIONS AUTHORITY</t>
         </is>
       </c>
       <c r="C96" s="18" t="inlineStr">
         <is>
-          <t>Ksh67,912,421.09</t>
+          <t>Ksh24,786,944.00</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>template</t>
         </is>
       </c>
     </row>
@@ -35777,12 +36403,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KENYA ACADEMY OF SPORTS</t>
+          <t>NATIONAL COUNCIL FOR LAW REPORTING</t>
         </is>
       </c>
       <c r="C97" s="18" t="inlineStr">
         <is>
-          <t>Ksh395,808,707.00</t>
+          <t>Ksh127,635,300.00</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
@@ -35797,17 +36423,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>COMMUNICATIONS AUTHORITY OF KENYA</t>
+          <t>JOMO KENYATTA FOUNDATION</t>
         </is>
       </c>
       <c r="C98" s="18" t="inlineStr">
         <is>
-          <t>Ksh1,118,814,997.00</t>
-        </is>
-      </c>
-      <c r="D98" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Ksh1,533,997,510.00</t>
+        </is>
+      </c>
+      <c r="D98" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -35817,12 +36443,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MEDIA COUNCIL OF KENYA</t>
+          <t>NUCLEAR POWER AND ENERGY AGENCY</t>
         </is>
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>Ksh295,559,876.97</t>
+          <t>Ksh265,915,508.00</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -35837,15 +36463,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>STATE DEPARTMENT FOR CHILDREN SERVICES</t>
-        </is>
-      </c>
-      <c r="C100" s="18" t="n">
-        <v>274052412</v>
-      </c>
-      <c r="D100" s="21" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>UGUNJA TECHNICAL AND VOCATIONAL COLLEGE</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>Ksh67,912,421.09</t>
+        </is>
+      </c>
+      <c r="D100" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -35855,17 +36483,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NATIONAL CANCER INSTITUTE OF KENYA</t>
-        </is>
-      </c>
-      <c r="C101" s="18" t="inlineStr">
-        <is>
-          <t>Ksh180,997,387.00</t>
-        </is>
-      </c>
-      <c r="D101" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>STATE DEPARTMENT FOR BASIC EDUCATION</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="n">
+        <v>177187729.3</v>
+      </c>
+      <c r="D101" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -35875,15 +36501,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LAKE VICTORIA NORTH WATER WORKS DEVELOPMENT AGENCY</t>
-        </is>
-      </c>
-      <c r="C102" s="18" t="n">
-        <v>1145429620</v>
-      </c>
-      <c r="D102" s="21" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>KENYA ACADEMY OF SPORTS</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
+        <is>
+          <t>Ksh395,808,707.00</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -35893,17 +36521,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KENYA CULTURAL CENTRE</t>
-        </is>
-      </c>
-      <c r="C103" s="18" t="inlineStr">
-        <is>
-          <t>Ksh132,794,835.68</t>
-        </is>
-      </c>
-      <c r="D103" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>WILDLIFE CLUBS OF KENYA</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="n">
+        <v>63424760</v>
+      </c>
+      <c r="D103" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -35913,15 +36539,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NORTHERN WATER WORKS DEVELOPMENT AGENCY</t>
-        </is>
-      </c>
-      <c r="C104" s="18" t="n">
-        <v>1734806300</v>
-      </c>
-      <c r="D104" s="21" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>COMMUNICATIONS AUTHORITY OF KENYA</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t>Ksh1,118,814,997.00</t>
+        </is>
+      </c>
+      <c r="D104" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -35931,17 +36559,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>UNIVERSITIES FUND</t>
-        </is>
-      </c>
-      <c r="C105" s="18" t="inlineStr">
-        <is>
-          <t>Ksh171,902,977.00</t>
-        </is>
-      </c>
-      <c r="D105" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>STATE DEPARTMENT FOR CHILDREN SERVICES</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="n">
+        <v>274052412</v>
+      </c>
+      <c r="D105" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -35951,12 +36577,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>UNCLAIMED FINANCIAL ASSETS AUTHORITY</t>
+          <t>NATIONAL CANCER INSTITUTE OF KENYA</t>
         </is>
       </c>
       <c r="C106" s="18" t="inlineStr">
         <is>
-          <t>Ksh285,262,248.00</t>
+          <t>Ksh180,997,387.00</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
@@ -35971,17 +36597,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TOM MBOYA UNIVERSITY</t>
-        </is>
-      </c>
-      <c r="C107" s="18" t="inlineStr">
-        <is>
-          <t>Ksh1,243,606,471.00</t>
-        </is>
-      </c>
-      <c r="D107" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>STATE DEPARTMENT FOR SPORTS</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="n">
+        <v>85998717</v>
+      </c>
+      <c r="D107" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -35991,17 +36615,15 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KENYA DAIRY BOARD</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="inlineStr">
-        <is>
-          <t>Ksh117,265,918.00</t>
-        </is>
-      </c>
-      <c r="D108" s="20" t="inlineStr">
-        <is>
-          <t>Doing</t>
+          <t>LAKE VICTORIA NORTH WATER WORKS DEVELOPMENT AGENCY</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="n">
+        <v>1145429620</v>
+      </c>
+      <c r="D108" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -36011,15 +36633,290 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
+          <t>KENYA CULTURAL CENTRE</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
+        <is>
+          <t>Ksh132,794,835.68</t>
+        </is>
+      </c>
+      <c r="D109" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NORTHERN WATER WORKS DEVELOPMENT AGENCY</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="n">
+        <v>1734806300</v>
+      </c>
+      <c r="D110" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>UNIVERSITIES FUND</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="inlineStr">
+        <is>
+          <t>Ksh171,902,977.00</t>
+        </is>
+      </c>
+      <c r="D111" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TANA AND ATHI RIVERS DEVELOPMENT AUTHORITY</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="n">
+        <v>192800000</v>
+      </c>
+      <c r="D112" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TOM MBOYA UNIVERSITY</t>
+        </is>
+      </c>
+      <c r="C113" s="18" t="inlineStr">
+        <is>
+          <t>Ksh1,243,606,471.00</t>
+        </is>
+      </c>
+      <c r="D113" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CHUKA UNIVERSITY</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="n">
+        <v>313544263</v>
+      </c>
+      <c r="D114" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>KENYA DAIRY BOARD</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="inlineStr">
+        <is>
+          <t>Ksh117,265,918.00</t>
+        </is>
+      </c>
+      <c r="D115" s="20" t="inlineStr">
+        <is>
+          <t>Doing</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>STATE DEPARTMENT FOR SCIENCE, RESEARCH AND INNOVATION</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="n">
+        <v>77551821</v>
+      </c>
+      <c r="D116" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TANA WATER WORKS DEVELOPMENT AGENCY</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="inlineStr">
+        <is>
+          <t>Ksh540,425,718.00</t>
+        </is>
+      </c>
+      <c r="D117" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
           <t>NAIROBI METROPOLITAN AREA TRANSPORT AUTHORITY</t>
         </is>
       </c>
-      <c r="C109" s="18" t="inlineStr">
+      <c r="C118" s="18" t="inlineStr">
         <is>
           <t>Ksh7,993,793.00</t>
         </is>
       </c>
-      <c r="D109" s="20" t="inlineStr">
+      <c r="D118" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>UNCLAIMED FINANCIAL ASSETS AUTHORITY</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="inlineStr">
+        <is>
+          <t>Ksh285,262,248.00</t>
+        </is>
+      </c>
+      <c r="D119" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>COUNCIL FOR LEGAL EDUCATION</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>Ksh95,593,383.00</t>
+        </is>
+      </c>
+      <c r="D120" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>COMMISSION ON REVENUE ALLOCATION</t>
+        </is>
+      </c>
+      <c r="C121" s="18" t="inlineStr">
+        <is>
+          <t>Ksh85,393,787.00</t>
+        </is>
+      </c>
+      <c r="D121" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>KENYA SCHOOL OF LAW</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="n">
+        <v>153454409</v>
+      </c>
+      <c r="D122" s="21" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>MEDIA COUNCIL OF KENYA</t>
+        </is>
+      </c>
+      <c r="C123" s="18" t="inlineStr">
+        <is>
+          <t>Ksh295,559,876.97</t>
+        </is>
+      </c>
+      <c r="D123" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -36036,7 +36933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36367,7 +37264,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4871 VIHIGA PUBLIC SERVICE AND ADMINSTRATION</t>
+          <t>4011  MURANGA - COUNTY ASSEMBLY</t>
         </is>
       </c>
     </row>
@@ -36377,7 +37274,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4814 KAKAMEGA - EDUCATION, SCIENCE AND TECHNOLOGY</t>
+          <t>4871 VIHIGA PUBLIC SERVICE AND ADMINSTRATION</t>
         </is>
       </c>
     </row>
@@ -36387,7 +37284,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3913 NYERI-FINANCE,ECONOMIC PLANNING AND ICT</t>
+          <t>4814 KAKAMEGA - EDUCATION, SCIENCE AND TECHNOLOGY</t>
         </is>
       </c>
     </row>
@@ -36397,7 +37294,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3916 NYERI-GENDER,YOUTH,SOCIAL SERVICES AND SPORTS</t>
+          <t>3913 NYERI-FINANCE,ECONOMIC PLANNING AND ICT</t>
         </is>
       </c>
     </row>
@@ -36407,7 +37304,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3927 NYERI   MUNICIPALITY</t>
+          <t>3916 NYERI-GENDER,YOUTH,SOCIAL SERVICES AND SPORTS</t>
         </is>
       </c>
     </row>
@@ -36417,7 +37314,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3924 NYERI-ROADS,TRANSPORT,PUBLIC WORKS,INFRASTRUCTURE AND ENERGY</t>
+          <t>3927 NYERI   MUNICIPALITY</t>
         </is>
       </c>
     </row>
@@ -36427,7 +37324,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3921 NYERI-WATER,ENVIRONMENT AND CLIMATE CHANGE</t>
+          <t>3924 NYERI-ROADS,TRANSPORT,PUBLIC WORKS,INFRASTRUCTURE AND ENERGY</t>
         </is>
       </c>
     </row>
@@ -36437,7 +37334,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4012 MURANGA - MINISTRY COUNTY COORDINATION AND ADMINSTRATION</t>
+          <t>3921 NYERI-WATER,ENVIRONMENT AND CLIMATE CHANGE</t>
         </is>
       </c>
     </row>
@@ -36447,7 +37344,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4867 VIHIGA COUNTY EXECUTIVE</t>
+          <t>4012 MURANGA - MINISTRY COUNTY COORDINATION AND ADMINSTRATION</t>
         </is>
       </c>
     </row>
@@ -36457,7 +37354,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3914 NYERI-LANDS,PHYSICAL PLANNING AND URBAN DEVELOPMENT</t>
+          <t>4867 VIHIGA COUNTY EXECUTIVE</t>
         </is>
       </c>
     </row>
@@ -36467,7 +37364,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3926 NYERI-OFFICE OF THE COUNTY ATTORNEY</t>
+          <t>3914 NYERI-LANDS,PHYSICAL PLANNING AND URBAN DEVELOPMENT</t>
         </is>
       </c>
     </row>
@@ -36477,7 +37374,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3915 NYERI-HEALTH SERVICES</t>
+          <t>3926 NYERI-OFFICE OF THE COUNTY ATTORNEY</t>
         </is>
       </c>
     </row>
@@ -36487,7 +37384,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3918  NYERI-AGRICULTURE,LIVESTOCK AND AQUACULTURE DEVELOPMENT</t>
+          <t>3915 NYERI-HEALTH SERVICES</t>
         </is>
       </c>
     </row>
@@ -36497,7 +37394,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3912 NYERI-OFFICE OF THE COUNTY SECRETARY</t>
+          <t>3918  NYERI-AGRICULTURE,LIVESTOCK AND AQUACULTURE DEVELOPMENT</t>
         </is>
       </c>
     </row>
@@ -36507,7 +37404,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3919 NYERI-TRADE,CO-OPERATIVES,CULTURE AND TOURISM</t>
+          <t>3912 NYERI-OFFICE OF THE COUNTY SECRETARY</t>
         </is>
       </c>
     </row>
@@ -36517,7 +37414,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3211 COUNTY ASSEMBLY OF LAMU</t>
+          <t>3919 NYERI-TRADE,CO-OPERATIVES,CULTURE AND TOURISM</t>
         </is>
       </c>
     </row>
@@ -36527,7 +37424,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4018 MURANGA - MINISTRY OF HEALTH AND SANITATION</t>
+          <t>3211 COUNTY ASSEMBLY OF LAMU</t>
         </is>
       </c>
     </row>
@@ -36537,7 +37434,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4431 NANDI - LANDS,PHYSICAL PLANNING, HOUSING ENVI,WATER,NATURAL RESOURCES/CLI</t>
+          <t>4018 MURANGA - MINISTRY OF HEALTH AND SANITATION</t>
         </is>
       </c>
     </row>
@@ -36547,7 +37444,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4430 NANDI - EDUCATION VOCATIONAL TRAINING AND SCHOLARSHIP</t>
+          <t>4431 NANDI - LANDS,PHYSICAL PLANNING, HOUSING ENVI,WATER,NATURAL RESOURCES/CLI</t>
         </is>
       </c>
     </row>
@@ -36557,7 +37454,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3917 NYERI-COUNTY PUBLIC SERVICE AND SOLID WASTE MANAGEMENT</t>
+          <t>4430 NANDI - EDUCATION VOCATIONAL TRAINING AND SCHOLARSHIP</t>
         </is>
       </c>
     </row>
@@ -36567,7 +37464,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4429 NANDI-SPORTS,YOUTH AFFAIRS,GENDER AND SOCIAL WELFARE ARTS</t>
+          <t>3917 NYERI-COUNTY PUBLIC SERVICE AND SOLID WASTE MANAGEMENT</t>
         </is>
       </c>
     </row>
@@ -36577,7 +37474,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3920 NYERI-EDUCATION,TRAINING AND DEVOLUTION</t>
+          <t>4429 NANDI-SPORTS,YOUTH AFFAIRS,GENDER AND SOCIAL WELFARE ARTS</t>
         </is>
       </c>
     </row>
@@ -36587,7 +37484,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4026 MURANG'A - MUNICIPALITY</t>
+          <t>3920 NYERI-EDUCATION,TRAINING AND DEVOLUTION</t>
         </is>
       </c>
     </row>
@@ -36597,7 +37494,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4029 MURANGA - MINISTRY OF PUBLIC SERVICE AND INFORMATION TECHNOLOGY COMMUNICATION</t>
+          <t>4026 MURANG'A - MUNICIPALITY</t>
         </is>
       </c>
     </row>
@@ -36607,7 +37504,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4015 MURANGA - MINISTRY OF TRANSPORT, WATER AND INFRASTRUCTURE</t>
+          <t>4029 MURANGA - MINISTRY OF PUBLIC SERVICE AND INFORMATION TECHNOLOGY COMMUNICATION</t>
         </is>
       </c>
     </row>
@@ -36617,7 +37514,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4414 NANDI - HEALTH</t>
+          <t>4015 MURANGA - MINISTRY OF TRANSPORT, WATER AND INFRASTRUCTURE</t>
         </is>
       </c>
     </row>
@@ -36627,7 +37524,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4469 BARINGO LANDS, HOUSING AND URBAN DEVELOPMENT</t>
+          <t>4414 NANDI - HEALTH</t>
         </is>
       </c>
     </row>
@@ -36637,7 +37534,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4423 NANDI - COUNTY ASSEMBLY</t>
+          <t>4469 BARINGO LANDS, HOUSING AND URBAN DEVELOPMENT</t>
         </is>
       </c>
     </row>
@@ -36647,7 +37544,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4061 COUNTY ASSEMBLY OF KIAMBU</t>
+          <t>4017 MURANGA - MINISTRY OF EDUCATION, INFORMATION TECHNOLOGY AND TOURISM</t>
         </is>
       </c>
     </row>
@@ -36667,7 +37564,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4028 MURANGA - MINISTRY OF ENVIRONMENT NATURAL RESOURCES WATER AND IRRIGATION</t>
+          <t>4519 LAIKIPIA WATER</t>
         </is>
       </c>
     </row>
@@ -36677,7 +37574,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4032 KENOL-MUNICIPALITY</t>
+          <t>4028 MURANGA - MINISTRY OF ENVIRONMENT NATURAL RESOURCES WATER AND IRRIGATION</t>
         </is>
       </c>
     </row>
@@ -36687,7 +37584,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4031 KANGARI - MUNICIPALITY</t>
+          <t>4163 WEST POKOT - ROADS, PUBLIC WORKS AND TRANSPORT</t>
         </is>
       </c>
     </row>
@@ -36697,7 +37594,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4919 COUNTY ASSEMBLY OF BUNGOMA</t>
+          <t>4032 KENOL-MUNICIPALITY</t>
         </is>
       </c>
     </row>
@@ -36707,7 +37604,87 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>4031 KANGARI - MUNICIPALITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>4919 COUNTY ASSEMBLY OF BUNGOMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>3816 MAKUENI FINANCE AND SOCIAL ECONOMIC PLANNING</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>4474 BARINGO KABARNET MUNICIPALITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>4061 COUNTY ASSEMBLY OF KIAMBU</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>COUNTY ASSEMBLY OF NYERI</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>3111 COUNTY ASSEMBLY OF KILIFI PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>4361 COUNTY ASSEMBLY OF ELGEYO MARAKWET PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>4423 NANDI - COUNTY ASSEMBLY</t>
         </is>
       </c>
     </row>
